--- a/3-Bases de Datos/BD_SKU_Codes.xlsx
+++ b/3-Bases de Datos/BD_SKU_Codes.xlsx
@@ -558,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1448"/>
+  <dimension ref="A1:B1447"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="18.75"/>
   <cols>
     <col width="12.28515625" customWidth="1" style="12" min="1" max="1"/>
@@ -11173,355 +11173,355 @@
     <row r="886">
       <c r="A886" s="4" t="inlineStr">
         <is>
-          <t>15E13D</t>
+          <t>15DD17</t>
         </is>
       </c>
       <c r="B886" s="5" t="inlineStr">
         <is>
-          <t>Magna CTX 100, 1000L HA</t>
+          <t>Magna CTX 320, 1000L EA</t>
         </is>
       </c>
     </row>
     <row r="887">
       <c r="A887" s="4" t="inlineStr">
         <is>
-          <t>15DD17</t>
+          <t>156FCC</t>
         </is>
       </c>
       <c r="B887" s="5" t="inlineStr">
         <is>
-          <t>Magna CTX 320, 1000L EA</t>
+          <t>Magna CTX 320, 1000L IB</t>
         </is>
       </c>
     </row>
     <row r="888">
       <c r="A888" s="4" t="inlineStr">
         <is>
-          <t>156FCC</t>
+          <t>15CDCE</t>
         </is>
       </c>
       <c r="B888" s="5" t="inlineStr">
         <is>
-          <t>Magna CTX 320, 1000L IB</t>
+          <t>Magna CTX 680 WT, 1000L E4</t>
         </is>
       </c>
     </row>
     <row r="889">
       <c r="A889" s="4" t="inlineStr">
         <is>
-          <t>15CDCE</t>
+          <t>158B12</t>
         </is>
       </c>
       <c r="B889" s="5" t="inlineStr">
         <is>
-          <t>Magna CTX 680 WT, 1000L E4</t>
+          <t>Magna PG 100, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="890">
       <c r="A890" s="4" t="inlineStr">
         <is>
-          <t>158B12</t>
+          <t>1573B0</t>
         </is>
       </c>
       <c r="B890" s="5" t="inlineStr">
         <is>
-          <t>Magna PG 100, 208L E4</t>
+          <t>Magna PM 220 S, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="891">
       <c r="A891" s="4" t="inlineStr">
         <is>
-          <t>1573B0</t>
+          <t>15866F</t>
         </is>
       </c>
       <c r="B891" s="5" t="inlineStr">
         <is>
-          <t>Magna PM 220 S, 208L E4</t>
+          <t>Magna PM 220 ZZ, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="892">
       <c r="A892" s="4" t="inlineStr">
         <is>
-          <t>15866F</t>
+          <t>157B63</t>
         </is>
       </c>
       <c r="B892" s="5" t="inlineStr">
         <is>
-          <t>Magna PM 220 ZZ, 208L E4</t>
+          <t>Magna PM 220, 1000L E4</t>
         </is>
       </c>
     </row>
     <row r="893">
       <c r="A893" s="4" t="inlineStr">
         <is>
-          <t>157B63</t>
+          <t>157B64</t>
         </is>
       </c>
       <c r="B893" s="5" t="inlineStr">
         <is>
-          <t>Magna PM 220, 1000L E4</t>
+          <t>Magna PM 220, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="894">
       <c r="A894" s="4" t="inlineStr">
         <is>
-          <t>157B64</t>
+          <t>1573CE</t>
         </is>
       </c>
       <c r="B894" s="5" t="inlineStr">
         <is>
-          <t>Magna PM 220, 208L E4</t>
+          <t>Magna PM 320 S, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="895">
       <c r="A895" s="4" t="inlineStr">
         <is>
-          <t>1573CE</t>
+          <t>156A6F</t>
         </is>
       </c>
       <c r="B895" s="5" t="inlineStr">
         <is>
-          <t>Magna PM 320 S, 208L E4</t>
+          <t>Magna PM 460 S, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="896">
       <c r="A896" s="4" t="inlineStr">
         <is>
-          <t>156A6F</t>
+          <t>15B596</t>
         </is>
       </c>
       <c r="B896" s="5" t="inlineStr">
         <is>
-          <t>Magna PM 460 S, 208L E4</t>
+          <t>Magna SW 220, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="897">
       <c r="A897" s="4" t="inlineStr">
         <is>
-          <t>15B596</t>
+          <t>1593BF</t>
         </is>
       </c>
       <c r="B897" s="5" t="inlineStr">
         <is>
-          <t>Magna SW 220, 208L E4</t>
+          <t>Magna SW 32, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="898">
       <c r="A898" s="4" t="inlineStr">
         <is>
-          <t>1593BF</t>
+          <t>1593BE</t>
         </is>
       </c>
       <c r="B898" s="5" t="inlineStr">
         <is>
-          <t>Magna SW 32, 208L E4</t>
+          <t>Magna SW 32, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="899">
       <c r="A899" s="4" t="inlineStr">
         <is>
-          <t>1593BE</t>
+          <t>15B5E4</t>
         </is>
       </c>
       <c r="B899" s="5" t="inlineStr">
         <is>
-          <t>Magna SW 32, 20L E4</t>
+          <t>Magna SW 68, 1000L E4</t>
         </is>
       </c>
     </row>
     <row r="900">
       <c r="A900" s="4" t="inlineStr">
         <is>
-          <t>15B5E4</t>
+          <t>1593F4</t>
         </is>
       </c>
       <c r="B900" s="5" t="inlineStr">
         <is>
-          <t>Magna SW 68, 1000L E4</t>
+          <t>Magna SW B 100, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="901">
       <c r="A901" s="4" t="inlineStr">
         <is>
-          <t>1593F4</t>
+          <t>158B9F</t>
         </is>
       </c>
       <c r="B901" s="5" t="inlineStr">
         <is>
-          <t>Magna SW B 100, 208L E4</t>
+          <t>Magna SW B 220, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="902">
       <c r="A902" s="4" t="inlineStr">
         <is>
-          <t>158B9F</t>
+          <t>158CFE</t>
         </is>
       </c>
       <c r="B902" s="5" t="inlineStr">
         <is>
-          <t>Magna SW B 220, 208L E4</t>
+          <t>Magna SW B 68, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="903">
       <c r="A903" s="4" t="inlineStr">
         <is>
-          <t>158CFE</t>
+          <t>158CFD</t>
         </is>
       </c>
       <c r="B903" s="5" t="inlineStr">
         <is>
-          <t>Magna SW B 68, 208L E4</t>
+          <t>Magna SW B 68, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="904">
       <c r="A904" s="4" t="inlineStr">
         <is>
-          <t>158CFD</t>
+          <t>159B9D</t>
         </is>
       </c>
       <c r="B904" s="5" t="inlineStr">
         <is>
-          <t>Magna SW B 68, 20L E4</t>
+          <t>Magna SW D 150, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="905">
       <c r="A905" s="4" t="inlineStr">
         <is>
-          <t>159B9D</t>
+          <t>159B9E</t>
         </is>
       </c>
       <c r="B905" s="5" t="inlineStr">
         <is>
-          <t>Magna SW D 150, 208L E4</t>
+          <t>Magna SW D 150, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="906">
       <c r="A906" s="4" t="inlineStr">
         <is>
-          <t>159B9E</t>
+          <t>159B9F</t>
         </is>
       </c>
       <c r="B906" s="5" t="inlineStr">
         <is>
-          <t>Magna SW D 150, 20L E4</t>
+          <t>Magna SW D 220, 1000L E4</t>
         </is>
       </c>
     </row>
     <row r="907">
       <c r="A907" s="4" t="inlineStr">
         <is>
-          <t>159B9F</t>
+          <t>159BA3</t>
         </is>
       </c>
       <c r="B907" s="5" t="inlineStr">
         <is>
-          <t>Magna SW D 220, 1000L E4</t>
+          <t>Magna SW D 220, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="908">
       <c r="A908" s="4" t="inlineStr">
         <is>
-          <t>159BA3</t>
+          <t>159BA0</t>
         </is>
       </c>
       <c r="B908" s="5" t="inlineStr">
         <is>
-          <t>Magna SW D 220, 208L E4</t>
+          <t>Magna SW D 220, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="909">
       <c r="A909" s="4" t="inlineStr">
         <is>
-          <t>159BA0</t>
+          <t>158F20</t>
         </is>
       </c>
       <c r="B909" s="5" t="inlineStr">
         <is>
-          <t>Magna SW D 220, 20L E4</t>
+          <t>Magna SW D 32, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="910">
       <c r="A910" s="4" t="inlineStr">
         <is>
-          <t>158F20</t>
+          <t>158F1D</t>
         </is>
       </c>
       <c r="B910" s="5" t="inlineStr">
         <is>
-          <t>Magna SW D 32, 208L E4</t>
+          <t>Magna SW D 32, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="911">
       <c r="A911" s="4" t="inlineStr">
         <is>
-          <t>158F1D</t>
+          <t>1584F5</t>
         </is>
       </c>
       <c r="B911" s="5" t="inlineStr">
         <is>
-          <t>Magna SW D 32, 20L E4</t>
+          <t>Magna SW D 68, 1000L E4</t>
         </is>
       </c>
     </row>
     <row r="912">
       <c r="A912" s="4" t="inlineStr">
         <is>
-          <t>1584F5</t>
+          <t>158A0B</t>
         </is>
       </c>
       <c r="B912" s="5" t="inlineStr">
         <is>
-          <t>Magna SW D 68, 1000L E4</t>
+          <t>Magna SW D 68, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="913">
       <c r="A913" s="4" t="inlineStr">
         <is>
-          <t>158A0B</t>
+          <t>158A08</t>
         </is>
       </c>
       <c r="B913" s="5" t="inlineStr">
         <is>
-          <t>Magna SW D 68, 208L E4</t>
+          <t>Magna SW D 68, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="914">
       <c r="A914" s="4" t="inlineStr">
         <is>
-          <t>158A08</t>
+          <t>15EEDE</t>
         </is>
       </c>
       <c r="B914" s="5" t="inlineStr">
         <is>
-          <t>Magna SW D 68, 20L E4</t>
+          <t>Moly Grease, 18K</t>
         </is>
       </c>
     </row>
     <row r="915">
       <c r="A915" s="4" t="inlineStr">
         <is>
-          <t>15EEDE</t>
+          <t>15047E</t>
         </is>
       </c>
       <c r="B915" s="5" t="inlineStr">
@@ -11533,6394 +11533,6382 @@
     <row r="916">
       <c r="A916" s="4" t="inlineStr">
         <is>
-          <t>15047E</t>
+          <t>15C6A9</t>
         </is>
       </c>
       <c r="B916" s="5" t="inlineStr">
         <is>
-          <t>Moly Grease, 18K</t>
+          <t>Molub-Alloy 100-2 HT, 180K AA</t>
         </is>
       </c>
     </row>
     <row r="917">
       <c r="A917" s="4" t="inlineStr">
         <is>
-          <t>15C6A9</t>
+          <t>15C6A7</t>
         </is>
       </c>
       <c r="B917" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy 100-2 HT, 180K AA</t>
+          <t>Molub-Alloy 100-2 HT, 1K KQ</t>
         </is>
       </c>
     </row>
     <row r="918">
       <c r="A918" s="4" t="inlineStr">
         <is>
-          <t>15C6A7</t>
+          <t>15C6AA</t>
         </is>
       </c>
       <c r="B918" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy 100-2 HT, 1K KQ</t>
+          <t>Molub-Alloy 100-2 HT, 5K AA</t>
         </is>
       </c>
     </row>
     <row r="919">
       <c r="A919" s="4" t="inlineStr">
         <is>
-          <t>15C6AA</t>
+          <t>14674A</t>
         </is>
       </c>
       <c r="B919" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy 100-2 HT, 5K AA</t>
+          <t>Molub-Alloy 243 Arctic, 18K E4</t>
         </is>
       </c>
     </row>
     <row r="920">
       <c r="A920" s="4" t="inlineStr">
         <is>
-          <t>14674A</t>
+          <t>15B080</t>
         </is>
       </c>
       <c r="B920" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy 243 Arctic, 18K E4</t>
+          <t>Molub-Alloy 243 Arctic, 50X.4K E4</t>
         </is>
       </c>
     </row>
     <row r="921">
       <c r="A921" s="4" t="inlineStr">
         <is>
-          <t>15B080</t>
+          <t>158A18</t>
         </is>
       </c>
       <c r="B921" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy 243 Arctic, 50X.4K E4</t>
+          <t>Molub-Alloy 370-2, 5X1K AA</t>
         </is>
       </c>
     </row>
     <row r="922">
       <c r="A922" s="4" t="inlineStr">
         <is>
-          <t>158A18</t>
+          <t>15D2FA</t>
         </is>
       </c>
       <c r="B922" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy 370-2, 5X1K AA</t>
+          <t>Molub-Alloy 6080/460-1.5, 12X.4K IA</t>
         </is>
       </c>
     </row>
     <row r="923">
       <c r="A923" s="4" t="inlineStr">
         <is>
-          <t>15D2FA</t>
+          <t>15D23A</t>
         </is>
       </c>
       <c r="B923" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy 6080/460-1.5, 12X.4K IA</t>
+          <t>Molub-Alloy 6080/460-1.5, 180K AA</t>
         </is>
       </c>
     </row>
     <row r="924">
       <c r="A924" s="4" t="inlineStr">
         <is>
-          <t>15D23A</t>
+          <t>155CC2</t>
         </is>
       </c>
       <c r="B924" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy 6080/460-1.5, 180K AA</t>
+          <t>Molub-Alloy 777-1 NG, 18K E4</t>
         </is>
       </c>
     </row>
     <row r="925">
       <c r="A925" s="4" t="inlineStr">
         <is>
-          <t>155CC2</t>
+          <t>156AA6</t>
         </is>
       </c>
       <c r="B925" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy 777-1 NG, 18K E4</t>
+          <t>Molub-Alloy 777-2 NG, 18K E4</t>
         </is>
       </c>
     </row>
     <row r="926">
       <c r="A926" s="4" t="inlineStr">
         <is>
-          <t>156AA6</t>
+          <t>156AA7</t>
         </is>
       </c>
       <c r="B926" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy 777-2 NG, 18K E4</t>
+          <t>Molub-Alloy 777-2 NG, 190K E4</t>
         </is>
       </c>
     </row>
     <row r="927">
       <c r="A927" s="4" t="inlineStr">
         <is>
-          <t>156AA7</t>
+          <t>15A368</t>
         </is>
       </c>
       <c r="B927" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy 777-2 NG, 190K E4</t>
+          <t>Molub-Alloy 860/220-1 ES, 190K AA</t>
         </is>
       </c>
     </row>
     <row r="928">
       <c r="A928" s="4" t="inlineStr">
         <is>
-          <t>15A368</t>
+          <t>15ACD5</t>
         </is>
       </c>
       <c r="B928" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy 860/220-1 ES, 190K AA</t>
+          <t>Molub-Alloy 860/220-2 ES, 18K AA</t>
         </is>
       </c>
     </row>
     <row r="929">
       <c r="A929" s="4" t="inlineStr">
         <is>
-          <t>15ACD5</t>
+          <t>15ACD8</t>
         </is>
       </c>
       <c r="B929" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy 860/220-2 ES, 18K AA</t>
+          <t>Molub-Alloy 860/220-2 ES, 52K AA</t>
         </is>
       </c>
     </row>
     <row r="930">
       <c r="A930" s="4" t="inlineStr">
         <is>
-          <t>15ACD8</t>
+          <t>15A3AD</t>
         </is>
       </c>
       <c r="B930" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy 860/220-2 ES, 52K AA</t>
+          <t>Molub-Alloy 860/460-2 ES, 190K AA</t>
         </is>
       </c>
     </row>
     <row r="931">
       <c r="A931" s="4" t="inlineStr">
         <is>
-          <t>15A3AD</t>
+          <t>15A3AF</t>
         </is>
       </c>
       <c r="B931" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy 860/460-2 ES, 190K AA</t>
+          <t>Molub-Alloy 860/460-2 ES, 52K AA</t>
         </is>
       </c>
     </row>
     <row r="932">
       <c r="A932" s="4" t="inlineStr">
         <is>
-          <t>15A3AF</t>
+          <t>1466EA</t>
         </is>
       </c>
       <c r="B932" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy 860/460-2 ES, 52K AA</t>
+          <t>Molub-Alloy 870-2, 190K E7</t>
         </is>
       </c>
     </row>
     <row r="933">
       <c r="A933" s="4" t="inlineStr">
         <is>
-          <t>1466EA</t>
+          <t>157DC9</t>
         </is>
       </c>
       <c r="B933" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy 870-2, 190K E7</t>
+          <t>Molub-Alloy Blanc, 50K E4</t>
         </is>
       </c>
     </row>
     <row r="934">
       <c r="A934" s="4" t="inlineStr">
         <is>
-          <t>157DC9</t>
+          <t>15AD65</t>
         </is>
       </c>
       <c r="B934" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy Blanc, 50K E4</t>
+          <t>Molub-Alloy Blanc, 5K E4</t>
         </is>
       </c>
     </row>
     <row r="935">
       <c r="A935" s="4" t="inlineStr">
         <is>
-          <t>15AD65</t>
+          <t>15B339</t>
         </is>
       </c>
       <c r="B935" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy Blanc, 5K E4</t>
+          <t>Molub-Alloy CH 22 Spray, 12X.4L HP</t>
         </is>
       </c>
     </row>
     <row r="936">
       <c r="A936" s="4" t="inlineStr">
         <is>
-          <t>15B339</t>
+          <t>156B8C</t>
         </is>
       </c>
       <c r="B936" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy CH 22 Spray, 12X.4L HP</t>
+          <t>Molub-Alloy CH 22, 60L E4</t>
         </is>
       </c>
     </row>
     <row r="937">
       <c r="A937" s="4" t="inlineStr">
         <is>
-          <t>156B8C</t>
+          <t>157FC4</t>
         </is>
       </c>
       <c r="B937" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy CH 22, 60L E4</t>
+          <t>Molub-Alloy GM  969/320, 180K E4</t>
         </is>
       </c>
     </row>
     <row r="938">
       <c r="A938" s="4" t="inlineStr">
         <is>
-          <t>157FC4</t>
+          <t>156CFD</t>
         </is>
       </c>
       <c r="B938" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy GM  969/320, 180K E4</t>
+          <t>Molub-Alloy GM 140/460, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="939">
       <c r="A939" s="4" t="inlineStr">
         <is>
-          <t>156CFD</t>
+          <t>156B88</t>
         </is>
       </c>
       <c r="B939" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy GM 140/460, 208L E4</t>
+          <t>Molub-Alloy GM 300s/1000, 60L E4</t>
         </is>
       </c>
     </row>
     <row r="940">
       <c r="A940" s="4" t="inlineStr">
         <is>
-          <t>156B88</t>
+          <t>156DF2</t>
         </is>
       </c>
       <c r="B940" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy GM 300s/1000, 60L E4</t>
+          <t>Molub-Alloy GM 90/220, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="941">
       <c r="A941" s="4" t="inlineStr">
         <is>
-          <t>156DF2</t>
+          <t>15A50F</t>
         </is>
       </c>
       <c r="B941" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy GM 90/220, 208L E4</t>
+          <t>Molub-Alloy OG 936 SF Hvy, 18K AA</t>
         </is>
       </c>
     </row>
     <row r="942">
       <c r="A942" s="4" t="inlineStr">
         <is>
-          <t>15A50F</t>
+          <t>15A511</t>
         </is>
       </c>
       <c r="B942" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy OG 936 SF Hvy, 18K AA</t>
+          <t>Molub-Alloy OG 936 SF Hvy, 190K AA</t>
         </is>
       </c>
     </row>
     <row r="943">
       <c r="A943" s="4" t="inlineStr">
         <is>
-          <t>15A511</t>
+          <t>15A513</t>
         </is>
       </c>
       <c r="B943" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy OG 936 SF Hvy, 190K AA</t>
+          <t>Molub-Alloy OG 936 SF Hvy, 55K AA</t>
         </is>
       </c>
     </row>
     <row r="944">
       <c r="A944" s="4" t="inlineStr">
         <is>
-          <t>15A513</t>
+          <t>15E1BA</t>
         </is>
       </c>
       <c r="B944" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy OG 936 SF Hvy, 55K AA</t>
+          <t>Molub-Alloy OG 936 SFH S , 12X.4L LH</t>
         </is>
       </c>
     </row>
     <row r="945">
       <c r="A945" s="4" t="inlineStr">
         <is>
-          <t>15E1BA</t>
+          <t>15E69E</t>
         </is>
       </c>
       <c r="B945" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy OG 936 SFH S , 12X.4L LH</t>
+          <t>Molub-Alloy Paste HT  20X.1K NJ</t>
         </is>
       </c>
     </row>
     <row r="946">
       <c r="A946" s="4" t="inlineStr">
         <is>
-          <t>15E69E</t>
+          <t>15B744</t>
         </is>
       </c>
       <c r="B946" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy Paste HT  20X.1K NJ</t>
+          <t>Molub-Alloy Paste HT, 5X1K BM</t>
         </is>
       </c>
     </row>
     <row r="947">
       <c r="A947" s="4" t="inlineStr">
         <is>
-          <t>15B744</t>
+          <t>15755E</t>
         </is>
       </c>
       <c r="B947" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy Paste HT, 5X1K BM</t>
+          <t>Molub-Alloy Paste MF, 20K AA</t>
         </is>
       </c>
     </row>
     <row r="948">
       <c r="A948" s="4" t="inlineStr">
         <is>
-          <t>15755E</t>
+          <t>15B73F</t>
         </is>
       </c>
       <c r="B948" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy Paste MF, 20K AA</t>
+          <t>Molub-Alloy Paste MF, 5X1K KL</t>
         </is>
       </c>
     </row>
     <row r="949">
       <c r="A949" s="4" t="inlineStr">
         <is>
-          <t>15B73F</t>
+          <t>15B6B8</t>
         </is>
       </c>
       <c r="B949" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy Paste MF, 5X1K KL</t>
+          <t>Molub-Alloy Paste PL, 5X1K E4</t>
         </is>
       </c>
     </row>
     <row r="950">
       <c r="A950" s="4" t="inlineStr">
         <is>
-          <t>15B6B8</t>
+          <t>15748C</t>
         </is>
       </c>
       <c r="B950" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy Paste PL, 5X1K E4</t>
+          <t>Molub-Alloy Paste TA, 20K AA</t>
         </is>
       </c>
     </row>
     <row r="951">
       <c r="A951" s="4" t="inlineStr">
         <is>
-          <t>15748C</t>
+          <t>15E15A</t>
         </is>
       </c>
       <c r="B951" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy Paste TA, 20K AA</t>
+          <t>Molub-Alloy Paste TA, 20X.1K F5</t>
         </is>
       </c>
     </row>
     <row r="952">
       <c r="A952" s="4" t="inlineStr">
         <is>
-          <t>15E15A</t>
+          <t>15B746</t>
         </is>
       </c>
       <c r="B952" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy Paste TA, 20X.1K F5</t>
+          <t>Molub-Alloy Paste TA, 5X1K JZ</t>
         </is>
       </c>
     </row>
     <row r="953">
       <c r="A953" s="4" t="inlineStr">
         <is>
-          <t>15B746</t>
+          <t>15B6AD</t>
         </is>
       </c>
       <c r="B953" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy Paste TA, 5X1K JZ</t>
+          <t>Molub-Alloy Paste White T, 20X.1K JW</t>
         </is>
       </c>
     </row>
     <row r="954">
       <c r="A954" s="4" t="inlineStr">
         <is>
-          <t>15B6AD</t>
+          <t>15AF92</t>
         </is>
       </c>
       <c r="B954" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy Paste White T, 20X.1K JW</t>
+          <t>Molub-Alloy Paste White T, 5K GQ</t>
         </is>
       </c>
     </row>
     <row r="955">
       <c r="A955" s="4" t="inlineStr">
         <is>
-          <t>15AF92</t>
+          <t>15B747</t>
         </is>
       </c>
       <c r="B955" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy Paste White T, 5K GQ</t>
+          <t>Molub-Alloy Paste White T, 5X1K N6</t>
         </is>
       </c>
     </row>
     <row r="956">
       <c r="A956" s="4" t="inlineStr">
         <is>
-          <t>15B747</t>
+          <t>15AD06</t>
         </is>
       </c>
       <c r="B956" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy Paste White T, 5X1K N6</t>
+          <t>MolubAlloy PasteWHS LN776, 5K E4</t>
         </is>
       </c>
     </row>
     <row r="957">
       <c r="A957" s="4" t="inlineStr">
         <is>
-          <t>15AD06</t>
+          <t>15950F</t>
         </is>
       </c>
       <c r="B957" s="5" t="inlineStr">
         <is>
-          <t>MolubAlloy PasteWHS LN776, 5K E4</t>
+          <t>Molub-Alloy Suspnsn HTGU, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="958">
       <c r="A958" s="4" t="inlineStr">
         <is>
-          <t>15950F</t>
+          <t>15E22D</t>
         </is>
       </c>
       <c r="B958" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy Suspnsn HTGU, 20L E4</t>
+          <t>Molub-Alloy TF Spray, 12X.4L LO</t>
         </is>
       </c>
     </row>
     <row r="959">
       <c r="A959" s="4" t="inlineStr">
         <is>
-          <t>15E22D</t>
+          <t>15E59A</t>
         </is>
       </c>
       <c r="B959" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy TF Spray, 12X.4L LO</t>
+          <t>Molub-Alloy6040/460-1 1/2, 182K EA</t>
         </is>
       </c>
     </row>
     <row r="960">
       <c r="A960" s="4" t="inlineStr">
         <is>
-          <t>15E59A</t>
+          <t>15E59B</t>
         </is>
       </c>
       <c r="B960" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy6040/460-1 1/2, 182K EA</t>
+          <t>Molub-Alloy6040/460-1 1/2, 20K EA</t>
         </is>
       </c>
     </row>
     <row r="961">
       <c r="A961" s="4" t="inlineStr">
         <is>
-          <t>15E59B</t>
+          <t>158F2F</t>
         </is>
       </c>
       <c r="B961" s="5" t="inlineStr">
         <is>
-          <t>Molub-Alloy6040/460-1 1/2, 20K EA</t>
+          <t>Optigear 100, 208L HN</t>
         </is>
       </c>
     </row>
     <row r="962">
       <c r="A962" s="4" t="inlineStr">
         <is>
-          <t>158F2F</t>
+          <t>158F2E</t>
         </is>
       </c>
       <c r="B962" s="5" t="inlineStr">
         <is>
-          <t>Optigear 100, 208L HN</t>
+          <t>Optigear 100, 20L N HA</t>
         </is>
       </c>
     </row>
     <row r="963">
       <c r="A963" s="4" t="inlineStr">
         <is>
-          <t>158F2E</t>
+          <t>158F30</t>
         </is>
       </c>
       <c r="B963" s="5" t="inlineStr">
         <is>
-          <t>Optigear 100, 20L N HA</t>
+          <t>Optigear 100, 55L HW</t>
         </is>
       </c>
     </row>
     <row r="964">
       <c r="A964" s="4" t="inlineStr">
         <is>
-          <t>158F30</t>
+          <t>157AC9</t>
         </is>
       </c>
       <c r="B964" s="5" t="inlineStr">
         <is>
-          <t>Optigear 100, 55L HW</t>
+          <t>Optigear 1100/220, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="965">
       <c r="A965" s="4" t="inlineStr">
         <is>
-          <t>157AC9</t>
+          <t>157ACC</t>
         </is>
       </c>
       <c r="B965" s="5" t="inlineStr">
         <is>
-          <t>Optigear 1100/220, 208L E4</t>
+          <t>Optigear 1100/220, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="966">
       <c r="A966" s="4" t="inlineStr">
         <is>
-          <t>157ACC</t>
+          <t>156DC0</t>
         </is>
       </c>
       <c r="B966" s="5" t="inlineStr">
         <is>
-          <t>Optigear 1100/220, 20L E4</t>
+          <t>Optigear 1100/320, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="967">
       <c r="A967" s="4" t="inlineStr">
         <is>
-          <t>156DC0</t>
+          <t>156DBE</t>
         </is>
       </c>
       <c r="B967" s="5" t="inlineStr">
         <is>
-          <t>Optigear 1100/320, 208L E4</t>
+          <t>Optigear 1100/320, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="968">
       <c r="A968" s="4" t="inlineStr">
         <is>
-          <t>156DBE</t>
+          <t>1587BC</t>
         </is>
       </c>
       <c r="B968" s="5" t="inlineStr">
         <is>
-          <t>Optigear 1100/320, 20L E4</t>
+          <t>Optigear 1100/460, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="969">
       <c r="A969" s="4" t="inlineStr">
         <is>
-          <t>1587BC</t>
+          <t>1587BB</t>
         </is>
       </c>
       <c r="B969" s="5" t="inlineStr">
         <is>
-          <t>Optigear 1100/460, 208L E4</t>
+          <t>Optigear 1100/460, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="970">
       <c r="A970" s="4" t="inlineStr">
         <is>
-          <t>1587BB</t>
+          <t>158F08</t>
         </is>
       </c>
       <c r="B970" s="5" t="inlineStr">
         <is>
-          <t>Optigear 1100/460, 20L E4</t>
+          <t>Optigear 150, 208L HW</t>
         </is>
       </c>
     </row>
     <row r="971">
       <c r="A971" s="4" t="inlineStr">
         <is>
-          <t>158F08</t>
+          <t>158F06</t>
         </is>
       </c>
       <c r="B971" s="5" t="inlineStr">
         <is>
-          <t>Optigear 150, 208L HW</t>
+          <t>Optigear 150, 20L HW</t>
         </is>
       </c>
     </row>
     <row r="972">
       <c r="A972" s="4" t="inlineStr">
         <is>
-          <t>158F06</t>
+          <t>158F0A</t>
         </is>
       </c>
       <c r="B972" s="5" t="inlineStr">
         <is>
-          <t>Optigear 150, 20L HW</t>
+          <t>Optigear 150, 55L HC</t>
         </is>
       </c>
     </row>
     <row r="973">
       <c r="A973" s="4" t="inlineStr">
         <is>
-          <t>158F0A</t>
+          <t>158EAD</t>
         </is>
       </c>
       <c r="B973" s="5" t="inlineStr">
         <is>
-          <t>Optigear 150, 55L HC</t>
+          <t>Optigear 220, 20L HW</t>
         </is>
       </c>
     </row>
     <row r="974">
       <c r="A974" s="4" t="inlineStr">
         <is>
-          <t>158EAD</t>
+          <t>158EB0</t>
         </is>
       </c>
       <c r="B974" s="5" t="inlineStr">
         <is>
-          <t>Optigear 220, 20L HW</t>
+          <t>Optigear 220, 55L KB</t>
         </is>
       </c>
     </row>
     <row r="975">
       <c r="A975" s="4" t="inlineStr">
         <is>
-          <t>158EB0</t>
+          <t>15C29D</t>
         </is>
       </c>
       <c r="B975" s="5" t="inlineStr">
         <is>
-          <t>Optigear 220, 55L KB</t>
+          <t>Optigear 320, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="976">
       <c r="A976" s="4" t="inlineStr">
         <is>
-          <t>15C29D</t>
+          <t>15C29B</t>
         </is>
       </c>
       <c r="B976" s="5" t="inlineStr">
         <is>
-          <t>Optigear 320, 208L AA</t>
+          <t>Optigear 320, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="977">
       <c r="A977" s="4" t="inlineStr">
         <is>
-          <t>15C29B</t>
+          <t>15DD85</t>
         </is>
       </c>
       <c r="B977" s="5" t="inlineStr">
         <is>
-          <t>Optigear 320, 20L AA</t>
+          <t>Optigear ALR X1, 208L EA</t>
         </is>
       </c>
     </row>
     <row r="978">
       <c r="A978" s="4" t="inlineStr">
         <is>
-          <t>15DD85</t>
+          <t>15DD86</t>
         </is>
       </c>
       <c r="B978" s="5" t="inlineStr">
         <is>
-          <t>Optigear ALR X1, 208L EA</t>
+          <t>Optigear ALR X1, 20L EA</t>
         </is>
       </c>
     </row>
     <row r="979">
       <c r="A979" s="4" t="inlineStr">
         <is>
-          <t>15DD86</t>
+          <t>153F56</t>
         </is>
       </c>
       <c r="B979" s="5" t="inlineStr">
         <is>
-          <t>Optigear ALR X1, 20L EA</t>
+          <t>Optigear BM 100, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="980">
       <c r="A980" s="4" t="inlineStr">
         <is>
-          <t>153F56</t>
+          <t>153F4D</t>
         </is>
       </c>
       <c r="B980" s="5" t="inlineStr">
         <is>
-          <t>Optigear BM 100, 208L AA</t>
+          <t>Optigear BM 100, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="981">
       <c r="A981" s="4" t="inlineStr">
         <is>
-          <t>153F4D</t>
+          <t>153FE4</t>
         </is>
       </c>
       <c r="B981" s="5" t="inlineStr">
         <is>
-          <t>Optigear BM 100, 20L AA</t>
+          <t>Optigear BM 150, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="982">
       <c r="A982" s="4" t="inlineStr">
         <is>
-          <t>153FE4</t>
+          <t>153FC2</t>
         </is>
       </c>
       <c r="B982" s="5" t="inlineStr">
         <is>
-          <t>Optigear BM 150, 208L AA</t>
+          <t>Optigear BM 220, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="983">
       <c r="A983" s="4" t="inlineStr">
         <is>
-          <t>153FC2</t>
+          <t>153FBE</t>
         </is>
       </c>
       <c r="B983" s="5" t="inlineStr">
         <is>
-          <t>Optigear BM 220, 208L AA</t>
+          <t>Optigear BM 220, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="984">
       <c r="A984" s="4" t="inlineStr">
         <is>
-          <t>153FBE</t>
+          <t>155C10</t>
         </is>
       </c>
       <c r="B984" s="5" t="inlineStr">
         <is>
-          <t>Optigear BM 220, 20L AA</t>
+          <t>Optigear BM 3000, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="985">
       <c r="A985" s="4" t="inlineStr">
         <is>
-          <t>155C10</t>
+          <t>15405E</t>
         </is>
       </c>
       <c r="B985" s="5" t="inlineStr">
         <is>
-          <t>Optigear BM 3000, 208L AA</t>
+          <t>Optigear BM 320, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="986">
       <c r="A986" s="4" t="inlineStr">
         <is>
-          <t>15405E</t>
+          <t>15404F</t>
         </is>
       </c>
       <c r="B986" s="5" t="inlineStr">
         <is>
-          <t>Optigear BM 320, 208L AA</t>
+          <t>Optigear BM 320, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="987">
       <c r="A987" s="4" t="inlineStr">
         <is>
-          <t>15404F</t>
+          <t>15407D</t>
         </is>
       </c>
       <c r="B987" s="5" t="inlineStr">
         <is>
-          <t>Optigear BM 320, 20L AA</t>
+          <t>Optigear BM 460, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="988">
       <c r="A988" s="4" t="inlineStr">
         <is>
-          <t>15407D</t>
+          <t>15406F</t>
         </is>
       </c>
       <c r="B988" s="5" t="inlineStr">
         <is>
-          <t>Optigear BM 460, 208L AA</t>
+          <t>Optigear BM 460, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="989">
       <c r="A989" s="4" t="inlineStr">
         <is>
-          <t>15406F</t>
+          <t>153F64</t>
         </is>
       </c>
       <c r="B989" s="5" t="inlineStr">
         <is>
-          <t>Optigear BM 460, 20L AA</t>
+          <t>Optigear BM 68, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="990">
       <c r="A990" s="4" t="inlineStr">
         <is>
-          <t>153F64</t>
+          <t>153F68</t>
         </is>
       </c>
       <c r="B990" s="5" t="inlineStr">
         <is>
-          <t>Optigear BM 68, 208L AA</t>
+          <t>Optigear BM 68, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="991">
       <c r="A991" s="4" t="inlineStr">
         <is>
-          <t>153F68</t>
+          <t>153FB9</t>
         </is>
       </c>
       <c r="B991" s="5" t="inlineStr">
         <is>
-          <t>Optigear BM 68, 20L AA</t>
+          <t>Optigear BM 680, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="992">
       <c r="A992" s="4" t="inlineStr">
         <is>
-          <t>153FB9</t>
+          <t>153FBC</t>
         </is>
       </c>
       <c r="B992" s="5" t="inlineStr">
         <is>
-          <t>Optigear BM 680, 208L AA</t>
+          <t>Optigear BM 680, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="993">
       <c r="A993" s="4" t="inlineStr">
         <is>
-          <t>153FBC</t>
+          <t>151F3D</t>
         </is>
       </c>
       <c r="B993" s="5" t="inlineStr">
         <is>
-          <t>Optigear BM 680, 20L AA</t>
+          <t>Optigear EP 100, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="994">
       <c r="A994" s="4" t="inlineStr">
         <is>
-          <t>151F3D</t>
+          <t>151F3E</t>
         </is>
       </c>
       <c r="B994" s="5" t="inlineStr">
         <is>
-          <t>Optigear EP 100, 208L E4</t>
+          <t>Optigear EP 100, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="995">
       <c r="A995" s="4" t="inlineStr">
         <is>
-          <t>151F3E</t>
+          <t>151F3A</t>
         </is>
       </c>
       <c r="B995" s="5" t="inlineStr">
         <is>
-          <t>Optigear EP 100, 20L E4</t>
+          <t>Optigear EP 150, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="996">
       <c r="A996" s="4" t="inlineStr">
         <is>
-          <t>151F3A</t>
+          <t>151F3B</t>
         </is>
       </c>
       <c r="B996" s="5" t="inlineStr">
         <is>
-          <t>Optigear EP 150, 208L E4</t>
+          <t>Optigear EP 150, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="997">
       <c r="A997" s="4" t="inlineStr">
         <is>
-          <t>151F3B</t>
+          <t>151F10</t>
         </is>
       </c>
       <c r="B997" s="5" t="inlineStr">
         <is>
-          <t>Optigear EP 150, 20L E4</t>
+          <t>Optigear EP 220, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="998">
       <c r="A998" s="4" t="inlineStr">
         <is>
-          <t>151F10</t>
+          <t>151F11</t>
         </is>
       </c>
       <c r="B998" s="5" t="inlineStr">
         <is>
-          <t>Optigear EP 220, 208L E4</t>
+          <t>Optigear EP 220, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="999">
       <c r="A999" s="4" t="inlineStr">
         <is>
-          <t>151F11</t>
+          <t>151F3F</t>
         </is>
       </c>
       <c r="B999" s="5" t="inlineStr">
         <is>
-          <t>Optigear EP 220, 20L E4</t>
+          <t>Optigear EP 32, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" s="4" t="inlineStr">
         <is>
-          <t>151F3F</t>
+          <t>151F4D</t>
         </is>
       </c>
       <c r="B1000" s="5" t="inlineStr">
         <is>
-          <t>Optigear EP 32, 20L E4</t>
+          <t>Optigear EP 320, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" s="4" t="inlineStr">
         <is>
-          <t>151F4D</t>
+          <t>151F4E</t>
         </is>
       </c>
       <c r="B1001" s="5" t="inlineStr">
         <is>
-          <t>Optigear EP 320, 208L E4</t>
+          <t>Optigear EP 320, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" s="4" t="inlineStr">
         <is>
-          <t>151F4E</t>
+          <t>151F45</t>
         </is>
       </c>
       <c r="B1002" s="5" t="inlineStr">
         <is>
-          <t>Optigear EP 320, 20L E4</t>
+          <t>Optigear EP 46, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" s="4" t="inlineStr">
         <is>
-          <t>151F45</t>
+          <t>151F4B</t>
         </is>
       </c>
       <c r="B1003" s="5" t="inlineStr">
         <is>
-          <t>Optigear EP 46, 208L E4</t>
+          <t>Optigear EP 68, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" s="4" t="inlineStr">
         <is>
-          <t>151F4B</t>
+          <t>151F4C</t>
         </is>
       </c>
       <c r="B1004" s="5" t="inlineStr">
         <is>
-          <t>Optigear EP 68, 208L E4</t>
+          <t>Optigear EP 68, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" s="4" t="inlineStr">
         <is>
-          <t>151F4C</t>
+          <t>15E631</t>
         </is>
       </c>
       <c r="B1005" s="5" t="inlineStr">
         <is>
-          <t>Optigear EP 68, 20L E4</t>
+          <t>Optigear RMO, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" s="4" t="inlineStr">
         <is>
-          <t>15E631</t>
+          <t>15E630</t>
         </is>
       </c>
       <c r="B1006" s="5" t="inlineStr">
         <is>
-          <t>Optigear RMO, 208L AA</t>
+          <t>Optigear RMO, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" s="4" t="inlineStr">
         <is>
-          <t>15E630</t>
+          <t>15B5AF</t>
         </is>
       </c>
       <c r="B1007" s="5" t="inlineStr">
         <is>
-          <t>Optigear RMO, 20L AA</t>
+          <t>Optigear Syn PD 220 ES, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" s="4" t="inlineStr">
         <is>
-          <t>15B5AF</t>
+          <t>15B5AE</t>
         </is>
       </c>
       <c r="B1008" s="5" t="inlineStr">
         <is>
-          <t>Optigear Syn PD 220 ES, 208L E4</t>
+          <t>Optigear Syn PD 220 ES, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" s="4" t="inlineStr">
         <is>
-          <t>15B5AE</t>
+          <t>15BB67</t>
         </is>
       </c>
       <c r="B1009" s="5" t="inlineStr">
         <is>
-          <t>Optigear Syn PD 220 ES, 20L E4</t>
+          <t>Optigear Syn PD 320 ES, 1000L E4</t>
         </is>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" s="4" t="inlineStr">
         <is>
-          <t>15BB67</t>
+          <t>15B67A</t>
         </is>
       </c>
       <c r="B1010" s="5" t="inlineStr">
         <is>
-          <t>Optigear Syn PD 320 ES, 1000L E4</t>
+          <t>Optigear Syn PD 320 ES, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" s="4" t="inlineStr">
         <is>
-          <t>15B67A</t>
+          <t>15B6A6</t>
         </is>
       </c>
       <c r="B1011" s="5" t="inlineStr">
         <is>
-          <t>Optigear Syn PD 320 ES, 208L E4</t>
+          <t>Optigear Syn PD 460 ES, 200L E4</t>
         </is>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" s="4" t="inlineStr">
         <is>
-          <t>15B6A6</t>
+          <t>15B6A4</t>
         </is>
       </c>
       <c r="B1012" s="5" t="inlineStr">
         <is>
-          <t>Optigear Syn PD 460 ES, 200L E4</t>
+          <t>Optigear Syn PD 680 ES, 200L E4</t>
         </is>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" s="4" t="inlineStr">
         <is>
-          <t>15B6A4</t>
+          <t>1575FE</t>
         </is>
       </c>
       <c r="B1013" s="5" t="inlineStr">
         <is>
-          <t>Optigear Syn PD 680 ES, 200L E4</t>
+          <t>Optigear Synth 800/1000, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" s="4" t="inlineStr">
         <is>
-          <t>1575FE</t>
+          <t>1573F7</t>
         </is>
       </c>
       <c r="B1014" s="5" t="inlineStr">
         <is>
-          <t>Optigear Synth 800/1000, 20L E4</t>
+          <t>Optigear Synth 800/150, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" s="4" t="inlineStr">
         <is>
-          <t>1573F7</t>
+          <t>1573F4</t>
         </is>
       </c>
       <c r="B1015" s="5" t="inlineStr">
         <is>
-          <t>Optigear Synth 800/150, 208L E4</t>
+          <t>Optigear Synth 800/150, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" s="4" t="inlineStr">
         <is>
-          <t>1573F4</t>
+          <t>1594B6</t>
         </is>
       </c>
       <c r="B1016" s="5" t="inlineStr">
         <is>
-          <t>Optigear Synth 800/150, 20L E4</t>
+          <t>Optigear Synth 800/1500, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" s="4" t="inlineStr">
         <is>
-          <t>1594B6</t>
+          <t>156F81</t>
         </is>
       </c>
       <c r="B1017" s="5" t="inlineStr">
         <is>
-          <t>Optigear Synth 800/1500, 20L E4</t>
+          <t>Optigear Synth 800/220, 1000L E4</t>
         </is>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" s="4" t="inlineStr">
         <is>
-          <t>156F81</t>
+          <t>156F85</t>
         </is>
       </c>
       <c r="B1018" s="5" t="inlineStr">
         <is>
-          <t>Optigear Synth 800/220, 1000L E4</t>
+          <t>Optigear Synth 800/220, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" s="4" t="inlineStr">
         <is>
-          <t>156F85</t>
+          <t>156F82</t>
         </is>
       </c>
       <c r="B1019" s="5" t="inlineStr">
         <is>
-          <t>Optigear Synth 800/220, 208L E4</t>
+          <t>Optigear Synth 800/220, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" s="4" t="inlineStr">
         <is>
-          <t>156F82</t>
+          <t>15D4EC</t>
         </is>
       </c>
       <c r="B1020" s="5" t="inlineStr">
         <is>
-          <t>Optigear Synth 800/220, 20L E4</t>
+          <t>Optigear Synth X 320 AD, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" s="4" t="inlineStr">
         <is>
-          <t>15D4EC</t>
+          <t>156BE6</t>
         </is>
       </c>
       <c r="B1021" s="5" t="inlineStr">
         <is>
-          <t>Optigear Synth X 320 AD, 20L E4</t>
+          <t>Optigear Synthet 1510/320, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" s="4" t="inlineStr">
         <is>
-          <t>156BE6</t>
+          <t>156BE5</t>
         </is>
       </c>
       <c r="B1022" s="5" t="inlineStr">
         <is>
-          <t>Optigear Synthet 1510/320, 208L E4</t>
+          <t>Optigear Synthet 1510/320, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" s="4" t="inlineStr">
         <is>
-          <t>156BE5</t>
+          <t>156BE7</t>
         </is>
       </c>
       <c r="B1023" s="5" t="inlineStr">
         <is>
-          <t>Optigear Synthet 1510/320, 20L E4</t>
+          <t>Optigear Synthet 1510/320, 900L E4</t>
         </is>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" s="4" t="inlineStr">
         <is>
-          <t>156BE7</t>
+          <t>1575A0</t>
         </is>
       </c>
       <c r="B1024" s="5" t="inlineStr">
         <is>
-          <t>Optigear Synthet 1510/320, 900L E4</t>
+          <t>Optigear Synthet 1710/320, 1000L E4</t>
         </is>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" s="4" t="inlineStr">
         <is>
-          <t>1575A0</t>
+          <t>1575A5</t>
         </is>
       </c>
       <c r="B1025" s="5" t="inlineStr">
         <is>
-          <t>Optigear Synthet 1710/320, 1000L E4</t>
+          <t>Optigear Synthet 1710/320, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" s="4" t="inlineStr">
         <is>
-          <t>1575A5</t>
+          <t>1575A1</t>
         </is>
       </c>
       <c r="B1026" s="5" t="inlineStr">
         <is>
-          <t>Optigear Synthet 1710/320, 208L E4</t>
+          <t>Optigear Synthet 1710/320, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" s="4" t="inlineStr">
         <is>
-          <t>1575A1</t>
+          <t>1576CB</t>
         </is>
       </c>
       <c r="B1027" s="5" t="inlineStr">
         <is>
-          <t>Optigear Synthet 1710/320, 20L E4</t>
+          <t>Optigear Synthet 800/100, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" s="4" t="inlineStr">
         <is>
-          <t>1576CB</t>
+          <t>1576C8</t>
         </is>
       </c>
       <c r="B1028" s="5" t="inlineStr">
         <is>
-          <t>Optigear Synthet 800/100, 208L E4</t>
+          <t>Optigear Synthet 800/100, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" s="4" t="inlineStr">
         <is>
-          <t>1576C8</t>
+          <t>1571AE</t>
         </is>
       </c>
       <c r="B1029" s="5" t="inlineStr">
         <is>
-          <t>Optigear Synthet 800/100, 20L E4</t>
+          <t>Optigear Synthetic 800/460, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" s="4" t="inlineStr">
         <is>
-          <t>1571AE</t>
+          <t>1571A9</t>
         </is>
       </c>
       <c r="B1030" s="5" t="inlineStr">
         <is>
-          <t>Optigear Synthetic 800/460, 208L E4</t>
+          <t>Optigear Synthetic 800/460, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" s="4" t="inlineStr">
         <is>
-          <t>1571A9</t>
+          <t>1540BE</t>
         </is>
       </c>
       <c r="B1031" s="5" t="inlineStr">
         <is>
-          <t>Optigear Synthetic 800/460, 20L E4</t>
+          <t>Optigear Synthetic A 320, 1000L AA</t>
         </is>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" s="4" t="inlineStr">
         <is>
-          <t>1540BE</t>
+          <t>1540C1</t>
         </is>
       </c>
       <c r="B1032" s="5" t="inlineStr">
         <is>
-          <t>Optigear Synthetic A 320, 1000L AA</t>
+          <t>Optigear Synthetic A 320, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" s="4" t="inlineStr">
         <is>
-          <t>1540C1</t>
+          <t>1512B2</t>
         </is>
       </c>
       <c r="B1033" s="5" t="inlineStr">
         <is>
-          <t>Optigear Synthetic A 320, 20L AA</t>
+          <t>Optigear Synthetic CT 320, 1000L E4</t>
         </is>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" s="4" t="inlineStr">
         <is>
-          <t>1512B2</t>
+          <t>15220A</t>
         </is>
       </c>
       <c r="B1034" s="5" t="inlineStr">
         <is>
-          <t>Optigear Synthetic CT 320, 1000L E4</t>
+          <t>Optigear Synthetic CT 320, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" s="4" t="inlineStr">
         <is>
-          <t>15220A</t>
+          <t>1512B3</t>
         </is>
       </c>
       <c r="B1035" s="5" t="inlineStr">
         <is>
-          <t>Optigear Synthetic CT 320, 208L E4</t>
+          <t>Optigear Synthetic CT 320, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" s="4" t="inlineStr">
         <is>
-          <t>1512B3</t>
+          <t>1540EF</t>
         </is>
       </c>
       <c r="B1036" s="5" t="inlineStr">
         <is>
-          <t>Optigear Synthetic CT 320, 20L E4</t>
+          <t>Optigear Synthetic RO 150, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" s="4" t="inlineStr">
         <is>
-          <t>1540EF</t>
+          <t>1540EE</t>
         </is>
       </c>
       <c r="B1037" s="5" t="inlineStr">
         <is>
-          <t>Optigear Synthetic RO 150, 208L E4</t>
+          <t>Optigear Synthetic RO 150, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" s="4" t="inlineStr">
         <is>
-          <t>1540EE</t>
+          <t>1563B9</t>
         </is>
       </c>
       <c r="B1038" s="5" t="inlineStr">
         <is>
-          <t>Optigear Synthetic RO 150, 20L E4</t>
+          <t>Optigear Synthetic RO 220, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" s="4" t="inlineStr">
         <is>
-          <t>1563B9</t>
+          <t>15A58F</t>
         </is>
       </c>
       <c r="B1039" s="5" t="inlineStr">
         <is>
-          <t>Optigear Synthetic RO 220, 208L E4</t>
+          <t>Optigear Synthetic X 320, 1000L AA</t>
         </is>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" s="4" t="inlineStr">
         <is>
-          <t>15A58F</t>
+          <t>15A593</t>
         </is>
       </c>
       <c r="B1040" s="5" t="inlineStr">
         <is>
-          <t>Optigear Synthetic X 320, 1000L AA</t>
+          <t>Optigear Synthetic X 320, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" s="4" t="inlineStr">
         <is>
-          <t>15A593</t>
+          <t>15A591</t>
         </is>
       </c>
       <c r="B1041" s="5" t="inlineStr">
         <is>
-          <t>Optigear Synthetic X 320, 208L AA</t>
+          <t>Optigear Synthetic X 320, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" s="4" t="inlineStr">
         <is>
-          <t>15A591</t>
+          <t>15A495</t>
         </is>
       </c>
       <c r="B1042" s="5" t="inlineStr">
         <is>
-          <t>Optigear Synthetic X 320, 20L AA</t>
+          <t>Optigear Synthetic X 460, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" s="4" t="inlineStr">
         <is>
-          <t>15A495</t>
+          <t>15A493</t>
         </is>
       </c>
       <c r="B1043" s="5" t="inlineStr">
         <is>
-          <t>Optigear Synthetic X 460, 208L AA</t>
+          <t>Optigear Synthetic X 460, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" s="4" t="inlineStr">
         <is>
-          <t>15A493</t>
+          <t>156BED</t>
         </is>
       </c>
       <c r="B1044" s="5" t="inlineStr">
         <is>
-          <t>Optigear Synthetic X 460, 20L AA</t>
+          <t>Optigear Synthetic800/320, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" s="4" t="inlineStr">
         <is>
-          <t>156BED</t>
+          <t>15962B</t>
         </is>
       </c>
       <c r="B1045" s="5" t="inlineStr">
         <is>
-          <t>Optigear Synthetic800/320, 20L E4</t>
+          <t>Optigear Synthetic800/680, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" s="4" t="inlineStr">
         <is>
-          <t>15962B</t>
+          <t>15D6B3</t>
         </is>
       </c>
       <c r="B1046" s="5" t="inlineStr">
         <is>
-          <t>Optigear Synthetic800/680, 20L E4</t>
+          <t>Optileb 2 Sil, 1K EA</t>
         </is>
       </c>
     </row>
     <row r="1047">
       <c r="A1047" s="4" t="inlineStr">
         <is>
-          <t>15D6B3</t>
+          <t>155FD8</t>
         </is>
       </c>
       <c r="B1047" s="5" t="inlineStr">
         <is>
-          <t>Optileb 2 Sil, 1K EA</t>
+          <t>Optileb AT 15, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1048">
       <c r="A1048" s="4" t="inlineStr">
         <is>
-          <t>155FD8</t>
+          <t>156C86</t>
         </is>
       </c>
       <c r="B1048" s="5" t="inlineStr">
         <is>
-          <t>Optileb AT 15, 20L AA</t>
+          <t>Optileb CH 150, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" s="4" t="inlineStr">
         <is>
-          <t>156C86</t>
+          <t>15B0FD</t>
         </is>
       </c>
       <c r="B1049" s="5" t="inlineStr">
         <is>
-          <t>Optileb CH 150, 20L E4</t>
+          <t>Optileb CH 150, 5L E4</t>
         </is>
       </c>
     </row>
     <row r="1050">
       <c r="A1050" s="4" t="inlineStr">
         <is>
-          <t>15B0FD</t>
+          <t>15E1BB</t>
         </is>
       </c>
       <c r="B1050" s="5" t="inlineStr">
         <is>
-          <t>Optileb CH 150, 5L E4</t>
+          <t>Optileb CH 1500 Spray, 12X.4L</t>
         </is>
       </c>
     </row>
     <row r="1051">
       <c r="A1051" s="4" t="inlineStr">
         <is>
-          <t>15E1BB</t>
+          <t>15725A</t>
         </is>
       </c>
       <c r="B1051" s="5" t="inlineStr">
         <is>
-          <t>Optileb CH 1500 Spray, 12X.4L</t>
+          <t>Optileb CH 1500, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" s="4" t="inlineStr">
         <is>
-          <t>15725A</t>
+          <t>15B61D</t>
         </is>
       </c>
       <c r="B1052" s="5" t="inlineStr">
         <is>
-          <t>Optileb CH 1500, 20L E4</t>
+          <t>Optileb CH 280 Spray, 12X.4L KM</t>
         </is>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" s="4" t="inlineStr">
         <is>
-          <t>15B61D</t>
+          <t>157BB0</t>
         </is>
       </c>
       <c r="B1053" s="5" t="inlineStr">
         <is>
-          <t>Optileb CH 280 Spray, 12X.4L KM</t>
+          <t>Optileb CH 280, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" s="4" t="inlineStr">
         <is>
-          <t>157BB0</t>
+          <t>15B536</t>
         </is>
       </c>
       <c r="B1054" s="5" t="inlineStr">
         <is>
-          <t>Optileb CH 280, 20L E4</t>
+          <t>Optileb CH 32 Spray, 12X.4L AA</t>
         </is>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" s="4" t="inlineStr">
         <is>
-          <t>15B536</t>
+          <t>1573ED</t>
         </is>
       </c>
       <c r="B1055" s="5" t="inlineStr">
         <is>
-          <t>Optileb CH 32 Spray, 12X.4L AA</t>
+          <t>Optileb CH 32, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1056">
       <c r="A1056" s="4" t="inlineStr">
         <is>
-          <t>1573ED</t>
+          <t>155B78</t>
         </is>
       </c>
       <c r="B1056" s="5" t="inlineStr">
         <is>
-          <t>Optileb CH 32, 20L E4</t>
+          <t>Optileb DAB 8, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" s="4" t="inlineStr">
         <is>
-          <t>155B78</t>
+          <t>155B76</t>
         </is>
       </c>
       <c r="B1057" s="5" t="inlineStr">
         <is>
-          <t>Optileb DAB 8, 208L E4</t>
+          <t>Optileb DAB 8, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1058">
       <c r="A1058" s="4" t="inlineStr">
         <is>
-          <t>155B76</t>
+          <t>15E1BC</t>
         </is>
       </c>
       <c r="B1058" s="5" t="inlineStr">
         <is>
-          <t>Optileb DAB 8, 20L E4</t>
+          <t>Optileb F&amp;D Spray, 12X.4L LK</t>
         </is>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" s="4" t="inlineStr">
         <is>
-          <t>15E1BC</t>
+          <t>157BED</t>
         </is>
       </c>
       <c r="B1059" s="5" t="inlineStr">
         <is>
-          <t>Optileb F&amp;D Spray, 12X.4L LK</t>
+          <t>Optileb GR 823-0, 18K AA</t>
         </is>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" s="4" t="inlineStr">
         <is>
-          <t>157BED</t>
+          <t>1576F5</t>
         </is>
       </c>
       <c r="B1060" s="5" t="inlineStr">
         <is>
-          <t>Optileb GR 823-0, 18K AA</t>
+          <t>Optileb GR 823-1, 18K AA</t>
         </is>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" s="4" t="inlineStr">
         <is>
-          <t>1576F5</t>
+          <t>1592F1</t>
         </is>
       </c>
       <c r="B1061" s="5" t="inlineStr">
         <is>
-          <t>Optileb GR 823-1, 18K AA</t>
+          <t>Optileb GR 823-2, 18K AA</t>
         </is>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" s="4" t="inlineStr">
         <is>
-          <t>1592F1</t>
+          <t>1592F3</t>
         </is>
       </c>
       <c r="B1062" s="5" t="inlineStr">
         <is>
-          <t>Optileb GR 823-2, 18K AA</t>
+          <t>Optileb GR 823-2, 190K AA</t>
         </is>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" s="4" t="inlineStr">
         <is>
-          <t>1592F3</t>
+          <t>15B17F</t>
         </is>
       </c>
       <c r="B1063" s="5" t="inlineStr">
         <is>
-          <t>Optileb GR 823-2, 190K AA</t>
+          <t>Optileb GR 823-2, 50X.4K KD</t>
         </is>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" s="4" t="inlineStr">
         <is>
-          <t>15B17F</t>
+          <t>1592F4</t>
         </is>
       </c>
       <c r="B1064" s="5" t="inlineStr">
         <is>
-          <t>Optileb GR 823-2, 50X.4K KD</t>
+          <t>Optileb GR 823-2, 52K AA</t>
         </is>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" s="4" t="inlineStr">
         <is>
-          <t>1592F4</t>
+          <t>15D691</t>
         </is>
       </c>
       <c r="B1065" s="5" t="inlineStr">
         <is>
-          <t>Optileb GR 823-2, 52K AA</t>
+          <t>Optileb GR 9830, 1K EA</t>
         </is>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" s="4" t="inlineStr">
         <is>
-          <t>15D691</t>
+          <t>159BF3</t>
         </is>
       </c>
       <c r="B1066" s="5" t="inlineStr">
         <is>
-          <t>Optileb GR 9830, 1K EA</t>
+          <t>Optileb GR FS 2, 20X.38K E4</t>
         </is>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" s="4" t="inlineStr">
         <is>
-          <t>159BF3</t>
+          <t>1579ED</t>
         </is>
       </c>
       <c r="B1067" s="5" t="inlineStr">
         <is>
-          <t>Optileb GR FS 2, 20X.38K E4</t>
+          <t>Optileb GR UF 00, 17K E4</t>
         </is>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" s="4" t="inlineStr">
         <is>
-          <t>1579ED</t>
+          <t>1579EC</t>
         </is>
       </c>
       <c r="B1068" s="5" t="inlineStr">
         <is>
-          <t>Optileb GR UF 00, 17K E4</t>
+          <t>Optileb GR UF 00, 180K E4</t>
         </is>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" s="4" t="inlineStr">
         <is>
-          <t>1579EC</t>
+          <t>15B09D</t>
         </is>
       </c>
       <c r="B1069" s="5" t="inlineStr">
         <is>
-          <t>Optileb GR UF 00, 180K E4</t>
+          <t>Optileb GR UF 00, 5K E4</t>
         </is>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" s="4" t="inlineStr">
         <is>
-          <t>15B09D</t>
+          <t>156CB8</t>
         </is>
       </c>
       <c r="B1070" s="5" t="inlineStr">
         <is>
-          <t>Optileb GR UF 00, 5K E4</t>
+          <t>Optileb GR UF 1, 180K E4</t>
         </is>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" s="4" t="inlineStr">
         <is>
-          <t>156CB8</t>
+          <t>156CB0</t>
         </is>
       </c>
       <c r="B1071" s="5" t="inlineStr">
         <is>
-          <t>Optileb GR UF 1, 180K E4</t>
+          <t>Optileb GR UF 1, 18K E4</t>
         </is>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" s="4" t="inlineStr">
         <is>
-          <t>156CB0</t>
+          <t>159DAD</t>
         </is>
       </c>
       <c r="B1072" s="5" t="inlineStr">
         <is>
-          <t>Optileb GR UF 1, 18K E4</t>
+          <t>Optileb GR UF 1, 20X.38K AA</t>
         </is>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" s="4" t="inlineStr">
         <is>
-          <t>159DAD</t>
+          <t>159F0C</t>
         </is>
       </c>
       <c r="B1073" s="5" t="inlineStr">
         <is>
-          <t>Optileb GR UF 1, 20X.38K AA</t>
+          <t>Optileb GR UF 1, 50K E4</t>
         </is>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" s="4" t="inlineStr">
         <is>
-          <t>159F0C</t>
+          <t>15ADC6</t>
         </is>
       </c>
       <c r="B1074" s="5" t="inlineStr">
         <is>
-          <t>Optileb GR UF 1, 50K E4</t>
+          <t>Optileb GR UF 1, 5K E4</t>
         </is>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" s="4" t="inlineStr">
         <is>
-          <t>15ADC6</t>
+          <t>15658F</t>
         </is>
       </c>
       <c r="B1075" s="5" t="inlineStr">
         <is>
-          <t>Optileb GR UF 1, 5K E4</t>
+          <t>Optileb GT 100, 20L N E4</t>
         </is>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" s="4" t="inlineStr">
         <is>
-          <t>15658F</t>
+          <t>15A235</t>
         </is>
       </c>
       <c r="B1076" s="5" t="inlineStr">
         <is>
-          <t>Optileb GT 100, 20L N E4</t>
+          <t>Optileb GT 150, 208L N E4</t>
         </is>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" s="4" t="inlineStr">
         <is>
-          <t>15A235</t>
+          <t>15A234</t>
         </is>
       </c>
       <c r="B1077" s="5" t="inlineStr">
         <is>
-          <t>Optileb GT 150, 208L N E4</t>
+          <t>Optileb GT 150, 20L N E4</t>
         </is>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" s="4" t="inlineStr">
         <is>
-          <t>15A234</t>
+          <t>15EA11</t>
         </is>
       </c>
       <c r="B1078" s="5" t="inlineStr">
         <is>
-          <t>Optileb GT 150, 20L N E4</t>
+          <t>Optileb GT 1800/220, 18L EA</t>
         </is>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" s="4" t="inlineStr">
         <is>
-          <t>15EA11</t>
+          <t>15656C</t>
         </is>
       </c>
       <c r="B1079" s="5" t="inlineStr">
         <is>
-          <t>Optileb GT 1800/220, 18L EA</t>
+          <t>Optileb GT 220, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" s="4" t="inlineStr">
         <is>
-          <t>15656C</t>
+          <t>15655F</t>
         </is>
       </c>
       <c r="B1080" s="5" t="inlineStr">
         <is>
-          <t>Optileb GT 220, 208L E4</t>
+          <t>Optileb GT 220, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" s="4" t="inlineStr">
         <is>
-          <t>15655F</t>
+          <t>15719F</t>
         </is>
       </c>
       <c r="B1081" s="5" t="inlineStr">
         <is>
-          <t>Optileb GT 220, 20L E4</t>
+          <t>Optileb GT 320, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" s="4" t="inlineStr">
         <is>
-          <t>15719F</t>
+          <t>15719C</t>
         </is>
       </c>
       <c r="B1082" s="5" t="inlineStr">
         <is>
-          <t>Optileb GT 320, 208L E4</t>
+          <t>Optileb GT 320, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" s="4" t="inlineStr">
         <is>
-          <t>15719C</t>
+          <t>1569C7</t>
         </is>
       </c>
       <c r="B1083" s="5" t="inlineStr">
         <is>
-          <t>Optileb GT 320, 20L E4</t>
+          <t>Optileb GT 460, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" s="4" t="inlineStr">
         <is>
-          <t>1569C7</t>
+          <t>1569C5</t>
         </is>
       </c>
       <c r="B1084" s="5" t="inlineStr">
         <is>
-          <t>Optileb GT 460, 208L E4</t>
+          <t>Optileb GT 460, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" s="4" t="inlineStr">
         <is>
-          <t>1569C5</t>
+          <t>1565F6</t>
         </is>
       </c>
       <c r="B1085" s="5" t="inlineStr">
         <is>
-          <t>Optileb GT 460, 20L E4</t>
+          <t>Optileb HY 32, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" s="4" t="inlineStr">
         <is>
-          <t>1565F6</t>
+          <t>1565F3</t>
         </is>
       </c>
       <c r="B1086" s="5" t="inlineStr">
         <is>
-          <t>Optileb HY 32, 208L E4</t>
+          <t>Optileb HY 32, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1087">
       <c r="A1087" s="4" t="inlineStr">
         <is>
-          <t>1565F3</t>
+          <t>15627A</t>
         </is>
       </c>
       <c r="B1087" s="5" t="inlineStr">
         <is>
-          <t>Optileb HY 32, 20L E4</t>
+          <t>Optileb HY 46, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" s="4" t="inlineStr">
         <is>
-          <t>15627A</t>
+          <t>15626D</t>
         </is>
       </c>
       <c r="B1088" s="5" t="inlineStr">
         <is>
-          <t>Optileb HY 46, 208L E4</t>
+          <t>Optileb HY 46, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" s="4" t="inlineStr">
         <is>
-          <t>15626D</t>
+          <t>14C5AD</t>
         </is>
       </c>
       <c r="B1089" s="5" t="inlineStr">
         <is>
-          <t>Optileb HY 46, 20L E4</t>
+          <t>Optileb HY 68, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" s="4" t="inlineStr">
         <is>
-          <t>14C5AD</t>
+          <t>14CBB6</t>
         </is>
       </c>
       <c r="B1090" s="5" t="inlineStr">
         <is>
-          <t>Optileb HY 68, 208L E4</t>
+          <t>Optileb HY 68, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" s="4" t="inlineStr">
         <is>
-          <t>14CBB6</t>
+          <t>15622E</t>
         </is>
       </c>
       <c r="B1091" s="5" t="inlineStr">
         <is>
-          <t>Optileb HY 68, 20L E4</t>
+          <t>Optileb V 100, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" s="4" t="inlineStr">
         <is>
-          <t>15622E</t>
+          <t>15E02D</t>
         </is>
       </c>
       <c r="B1092" s="5" t="inlineStr">
         <is>
-          <t>Optileb V 100, 20L E4</t>
+          <t>Optileb V 46, 20L EA</t>
         </is>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" s="4" t="inlineStr">
         <is>
-          <t>15E02D</t>
+          <t>146A32</t>
         </is>
       </c>
       <c r="B1093" s="5" t="inlineStr">
         <is>
-          <t>Optileb V 46, 20L EA</t>
+          <t>Optileb VAS, 17K E7</t>
         </is>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" s="4" t="inlineStr">
         <is>
-          <t>146A32</t>
+          <t>1583BB</t>
         </is>
       </c>
       <c r="B1094" s="5" t="inlineStr">
         <is>
-          <t>Optileb VAS, 17K E7</t>
+          <t>Optileb WOM 14, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" s="4" t="inlineStr">
         <is>
-          <t>1583BB</t>
+          <t>1583B9</t>
         </is>
       </c>
       <c r="B1095" s="5" t="inlineStr">
         <is>
-          <t>Optileb WOM 14, 208L AA</t>
+          <t>Optileb WOM 14, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" s="4" t="inlineStr">
         <is>
-          <t>1583B9</t>
+          <t>156EFF</t>
         </is>
       </c>
       <c r="B1096" s="5" t="inlineStr">
         <is>
-          <t>Optileb WOM 14, 20L AA</t>
+          <t>Optileb WOM 24, 208L HD</t>
         </is>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" s="4" t="inlineStr">
         <is>
-          <t>156EFF</t>
+          <t>1583F6</t>
         </is>
       </c>
       <c r="B1097" s="5" t="inlineStr">
         <is>
-          <t>Optileb WOM 24, 208L HD</t>
+          <t>Optileb WOM 65, 1000L E4</t>
         </is>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" s="4" t="inlineStr">
         <is>
-          <t>1583F6</t>
+          <t>1583F8</t>
         </is>
       </c>
       <c r="B1098" s="5" t="inlineStr">
         <is>
-          <t>Optileb WOM 65, 1000L E4</t>
+          <t>Optileb WOM 65, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" s="4" t="inlineStr">
         <is>
-          <t>1583F8</t>
+          <t>1583F7</t>
         </is>
       </c>
       <c r="B1099" s="5" t="inlineStr">
         <is>
-          <t>Optileb WOM 65, 208L E4</t>
+          <t>Optileb WOM 65, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" s="4" t="inlineStr">
         <is>
-          <t>1583F7</t>
+          <t>157DAD</t>
         </is>
       </c>
       <c r="B1100" s="5" t="inlineStr">
         <is>
-          <t>Optileb WOM 65, 20L E4</t>
+          <t>Optitemp 2 LN 584 LO, 180K E4</t>
         </is>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" s="4" t="inlineStr">
         <is>
-          <t>157DAD</t>
+          <t>157DAC</t>
         </is>
       </c>
       <c r="B1101" s="5" t="inlineStr">
         <is>
-          <t>Optitemp 2 LN 584 LO, 180K E4</t>
+          <t>Optitemp 2 LN 584 LO, 18K E4</t>
         </is>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" s="4" t="inlineStr">
         <is>
-          <t>157DAC</t>
+          <t>14E35D</t>
         </is>
       </c>
       <c r="B1102" s="5" t="inlineStr">
         <is>
-          <t>Optitemp 2 LN 584 LO, 18K E4</t>
+          <t>Optitemp BT 1LF, 50K E4</t>
         </is>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" s="4" t="inlineStr">
         <is>
-          <t>14E35D</t>
+          <t>1593AD</t>
         </is>
       </c>
       <c r="B1103" s="5" t="inlineStr">
         <is>
-          <t>Optitemp BT 1LF, 50K E4</t>
+          <t>Optitemp FLF 1N, 50K E4</t>
         </is>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" s="4" t="inlineStr">
         <is>
-          <t>1593AD</t>
+          <t>14DA66</t>
         </is>
       </c>
       <c r="B1104" s="5" t="inlineStr">
         <is>
-          <t>Optitemp FLF 1N, 50K E4</t>
+          <t>Optitemp HT 1LF NG, 180K E4</t>
         </is>
       </c>
     </row>
     <row r="1105">
       <c r="A1105" s="4" t="inlineStr">
         <is>
-          <t>14DA66</t>
+          <t>14E83E</t>
         </is>
       </c>
       <c r="B1105" s="5" t="inlineStr">
         <is>
-          <t>Optitemp HT 1LF NG, 180K E4</t>
+          <t>Optitemp LG 0 (G), 17K E4</t>
         </is>
       </c>
     </row>
     <row r="1106">
       <c r="A1106" s="4" t="inlineStr">
         <is>
-          <t>14E83E</t>
+          <t>14E867</t>
         </is>
       </c>
       <c r="B1106" s="5" t="inlineStr">
         <is>
-          <t>Optitemp LG 0 (G), 17K E4</t>
+          <t>Optitemp LG 2 (G), 170K E4</t>
         </is>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" s="4" t="inlineStr">
         <is>
-          <t>14E867</t>
+          <t>15A3A1</t>
         </is>
       </c>
       <c r="B1107" s="5" t="inlineStr">
         <is>
-          <t>Optitemp LG 2 (G), 170K E4</t>
+          <t>Optitemp LG 2 (G), 48K E4</t>
         </is>
       </c>
     </row>
     <row r="1108">
       <c r="A1108" s="4" t="inlineStr">
         <is>
-          <t>15A3A1</t>
+          <t>15A3FE</t>
         </is>
       </c>
       <c r="B1108" s="5" t="inlineStr">
         <is>
-          <t>Optitemp LG 2 (G), 48K E4</t>
+          <t>Optitemp LG 2 (G), 5X1K E4</t>
         </is>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" s="4" t="inlineStr">
         <is>
-          <t>15A3FE</t>
+          <t>15A3C2</t>
         </is>
       </c>
       <c r="B1109" s="5" t="inlineStr">
         <is>
-          <t>Optitemp LG 2 (G), 5X1K E4</t>
+          <t>Optitemp PG 1.5, 180K AA</t>
         </is>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" s="4" t="inlineStr">
         <is>
-          <t>15A3C2</t>
+          <t>155B65</t>
         </is>
       </c>
       <c r="B1110" s="5" t="inlineStr">
         <is>
-          <t>Optitemp PG 1.5, 180K AA</t>
+          <t>Optitemp PU 035/4, 18K E4</t>
         </is>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" s="4" t="inlineStr">
         <is>
-          <t>155B65</t>
+          <t>1583F0</t>
         </is>
       </c>
       <c r="B1111" s="5" t="inlineStr">
         <is>
-          <t>Optitemp PU 035/4, 18K E4</t>
+          <t>Optitemp RB 2, 17K E4</t>
         </is>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" s="4" t="inlineStr">
         <is>
-          <t>1583F0</t>
+          <t>1583F3</t>
         </is>
       </c>
       <c r="B1112" s="5" t="inlineStr">
         <is>
-          <t>Optitemp RB 2, 17K E4</t>
+          <t>Optitemp RB 2, 5X1K E4</t>
         </is>
       </c>
     </row>
     <row r="1113">
       <c r="A1113" s="4" t="inlineStr">
         <is>
-          <t>1583F3</t>
+          <t>1554B2</t>
         </is>
       </c>
       <c r="B1113" s="5" t="inlineStr">
         <is>
-          <t>Optitemp RB 2, 5X1K E4</t>
+          <t>Optitemp XBT1LF, 170K E4</t>
         </is>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" s="4" t="inlineStr">
         <is>
-          <t>1554B2</t>
+          <t>15854F</t>
         </is>
       </c>
       <c r="B1114" s="5" t="inlineStr">
         <is>
-          <t>Optitemp XBT1LF, 170K E4</t>
+          <t>Perfecto HT 2, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" s="4" t="inlineStr">
         <is>
-          <t>15854F</t>
+          <t>134952</t>
         </is>
       </c>
       <c r="B1115" s="5" t="inlineStr">
         <is>
-          <t>Perfecto HT 2, 208L AA</t>
+          <t>Perfecto HT 5, 1000L E4</t>
         </is>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" s="4" t="inlineStr">
         <is>
-          <t>134952</t>
+          <t>14AEC6</t>
         </is>
       </c>
       <c r="B1116" s="5" t="inlineStr">
         <is>
-          <t>Perfecto HT 5, 1000L E4</t>
+          <t>Perfecto HT 5, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" s="4" t="inlineStr">
         <is>
-          <t>14AEC6</t>
+          <t>14F561</t>
         </is>
       </c>
       <c r="B1117" s="5" t="inlineStr">
         <is>
-          <t>Perfecto HT 5, 208L E4</t>
+          <t>Perfecto HT 5, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" s="4" t="inlineStr">
         <is>
-          <t>14F561</t>
+          <t>217C78</t>
         </is>
       </c>
       <c r="B1118" s="5" t="inlineStr">
         <is>
-          <t>Perfecto HT 5, 20L E4</t>
+          <t>Perfecto HT 5, IBC Bulk Cont</t>
         </is>
       </c>
     </row>
     <row r="1119">
       <c r="A1119" s="4" t="inlineStr">
         <is>
-          <t>217C78</t>
+          <t>156B10</t>
         </is>
       </c>
       <c r="B1119" s="5" t="inlineStr">
         <is>
-          <t>Perfecto HT 5, IBC Bulk Cont</t>
+          <t>Perfecto HTS 16, 208L HW</t>
         </is>
       </c>
     </row>
     <row r="1120">
       <c r="A1120" s="4" t="inlineStr">
         <is>
-          <t>156B10</t>
+          <t>14F577</t>
         </is>
       </c>
       <c r="B1120" s="5" t="inlineStr">
         <is>
-          <t>Perfecto HTS 16, 208L HW</t>
+          <t>Perfecto SN 46, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1121">
       <c r="A1121" s="4" t="inlineStr">
         <is>
-          <t>14F577</t>
+          <t>158C17</t>
         </is>
       </c>
       <c r="B1121" s="5" t="inlineStr">
         <is>
-          <t>Perfecto SN 46, 208L E4</t>
+          <t>Perfecto TR UN, 208L HG</t>
         </is>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" s="4" t="inlineStr">
         <is>
-          <t>158C17</t>
+          <t>158C18</t>
         </is>
       </c>
       <c r="B1122" s="5" t="inlineStr">
         <is>
-          <t>Perfecto TR UN, 208L HG</t>
+          <t>Perfecto TR UN, 20L HG</t>
         </is>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" s="4" t="inlineStr">
         <is>
-          <t>158C18</t>
+          <t>15D55C</t>
         </is>
       </c>
       <c r="B1123" s="5" t="inlineStr">
         <is>
-          <t>Perfecto TR UN, 20L HG</t>
+          <t>Perfecto X 100, 208L EA</t>
         </is>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" s="4" t="inlineStr">
         <is>
-          <t>15D55C</t>
+          <t>15D55B</t>
         </is>
       </c>
       <c r="B1124" s="5" t="inlineStr">
         <is>
-          <t>Perfecto X 100, 208L EA</t>
+          <t>Perfecto X 100, 20L EA</t>
         </is>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" s="4" t="inlineStr">
         <is>
-          <t>15D55B</t>
+          <t>157ADE</t>
         </is>
       </c>
       <c r="B1125" s="5" t="inlineStr">
         <is>
-          <t>Perfecto X 100, 20L EA</t>
+          <t>Perfecto X 32, 1000L E4</t>
         </is>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" s="4" t="inlineStr">
         <is>
-          <t>157ADE</t>
+          <t>157ADF</t>
         </is>
       </c>
       <c r="B1126" s="5" t="inlineStr">
         <is>
-          <t>Perfecto X 32, 1000L E4</t>
+          <t>Perfecto X 32, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1127">
       <c r="A1127" s="4" t="inlineStr">
         <is>
-          <t>157ADF</t>
+          <t>15D5C3</t>
         </is>
       </c>
       <c r="B1127" s="5" t="inlineStr">
         <is>
-          <t>Perfecto X 32, 208L E4</t>
+          <t>Perfecto X 32, 20L EA</t>
         </is>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" s="4" t="inlineStr">
         <is>
-          <t>15D5C3</t>
+          <t>21754E</t>
         </is>
       </c>
       <c r="B1128" s="5" t="inlineStr">
         <is>
-          <t>Perfecto X 32, 20L EA</t>
+          <t>Perfecto X 32, Bulk</t>
         </is>
       </c>
     </row>
     <row r="1129">
       <c r="A1129" s="4" t="inlineStr">
         <is>
-          <t>21754E</t>
+          <t>1562DC</t>
         </is>
       </c>
       <c r="B1129" s="5" t="inlineStr">
         <is>
-          <t>Perfecto X 32, Bulk</t>
+          <t>Perfecto X 46, 1000L N E4</t>
         </is>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" s="4" t="inlineStr">
         <is>
-          <t>1562DC</t>
+          <t>1562DD</t>
         </is>
       </c>
       <c r="B1130" s="5" t="inlineStr">
         <is>
-          <t>Perfecto X 46, 1000L N E4</t>
+          <t>Perfecto X 46, 208L N E4</t>
         </is>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" s="4" t="inlineStr">
         <is>
-          <t>1562DD</t>
+          <t>15D5C9</t>
         </is>
       </c>
       <c r="B1131" s="5" t="inlineStr">
         <is>
-          <t>Perfecto X 46, 208L N E4</t>
+          <t>Perfecto X 46, 20L EA</t>
         </is>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" s="4" t="inlineStr">
         <is>
-          <t>15D5C9</t>
+          <t>21754D</t>
         </is>
       </c>
       <c r="B1132" s="5" t="inlineStr">
         <is>
-          <t>Perfecto X 46, 20L EA</t>
+          <t>Perfecto X 46, Bulk</t>
         </is>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" s="4" t="inlineStr">
         <is>
-          <t>21754D</t>
+          <t>15D5CB</t>
         </is>
       </c>
       <c r="B1133" s="5" t="inlineStr">
         <is>
-          <t>Perfecto X 46, Bulk</t>
+          <t>Perfecto X 68, 1000L EA</t>
         </is>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" s="4" t="inlineStr">
         <is>
-          <t>15D5CB</t>
+          <t>15064A</t>
         </is>
       </c>
       <c r="B1134" s="5" t="inlineStr">
         <is>
-          <t>Perfecto X 68, 1000L EA</t>
+          <t>Perfecto X 68, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" s="4" t="inlineStr">
         <is>
-          <t>15064A</t>
+          <t>15D5CC</t>
         </is>
       </c>
       <c r="B1135" s="5" t="inlineStr">
         <is>
-          <t>Perfecto X 68, 208L E4</t>
+          <t>Perfecto X 68, 20L EA</t>
         </is>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" s="4" t="inlineStr">
         <is>
-          <t>15D5CC</t>
+          <t>1506FD</t>
         </is>
       </c>
       <c r="B1136" s="5" t="inlineStr">
         <is>
-          <t>Perfecto X 68, 20L EA</t>
+          <t>Perfecto XEP 32, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1137">
       <c r="A1137" s="4" t="inlineStr">
         <is>
-          <t>1506FD</t>
+          <t>15E5E6</t>
         </is>
       </c>
       <c r="B1137" s="5" t="inlineStr">
         <is>
-          <t>Perfecto XEP 32, 208L E4</t>
+          <t>Perfecto XEP 46, 208L 1E</t>
         </is>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" s="4" t="inlineStr">
         <is>
-          <t>15E5E6</t>
+          <t>155EF8</t>
         </is>
       </c>
       <c r="B1138" s="5" t="inlineStr">
         <is>
-          <t>Perfecto XEP 46, 208L 1E</t>
+          <t>Perfecto XPG 32, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" s="4" t="inlineStr">
         <is>
-          <t>155EF8</t>
+          <t>15921A</t>
         </is>
       </c>
       <c r="B1139" s="5" t="inlineStr">
         <is>
-          <t>Perfecto XPG 32, 208L E4</t>
+          <t>Rustilo 181, 200L AD</t>
         </is>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" s="4" t="inlineStr">
         <is>
-          <t>15921A</t>
+          <t>1554C1</t>
         </is>
       </c>
       <c r="B1140" s="5" t="inlineStr">
         <is>
-          <t>Rustilo 181, 200L AD</t>
+          <t>Rustilo 4135 HF, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" s="4" t="inlineStr">
         <is>
-          <t>1554C1</t>
+          <t>1554BF</t>
         </is>
       </c>
       <c r="B1141" s="5" t="inlineStr">
         <is>
-          <t>Rustilo 4135 HF, 208L AA</t>
+          <t>Rustilo 4135 HF, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" s="4" t="inlineStr">
         <is>
-          <t>1554BF</t>
+          <t>1572DC</t>
         </is>
       </c>
       <c r="B1142" s="5" t="inlineStr">
         <is>
-          <t>Rustilo 4135 HF, 20L AA</t>
+          <t>Rustilo 5905, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" s="4" t="inlineStr">
         <is>
-          <t>1572DC</t>
+          <t>15633F</t>
         </is>
       </c>
       <c r="B1143" s="5" t="inlineStr">
         <is>
-          <t>Rustilo 5905, 208L AA</t>
+          <t>Rustilo 612, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" s="4" t="inlineStr">
         <is>
-          <t>15633F</t>
+          <t>15633C</t>
         </is>
       </c>
       <c r="B1144" s="5" t="inlineStr">
         <is>
-          <t>Rustilo 612, 208L AA</t>
+          <t>Rustilo 612, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" s="4" t="inlineStr">
         <is>
-          <t>15633C</t>
+          <t>15B7AC</t>
         </is>
       </c>
       <c r="B1145" s="5" t="inlineStr">
         <is>
-          <t>Rustilo 612, 20L AA</t>
+          <t>Rustilo 630, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" s="4" t="inlineStr">
         <is>
-          <t>15B7AC</t>
+          <t>1564A9</t>
         </is>
       </c>
       <c r="B1146" s="5" t="inlineStr">
         <is>
-          <t>Rustilo 630, 208L AA</t>
+          <t>Rustilo 652, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" s="4" t="inlineStr">
         <is>
-          <t>1564A9</t>
+          <t>15761E</t>
         </is>
       </c>
       <c r="B1147" s="5" t="inlineStr">
         <is>
-          <t>Rustilo 652, 208L E4</t>
+          <t>Rustilo 66 VCI, 18L AA</t>
         </is>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" s="4" t="inlineStr">
         <is>
-          <t>15761E</t>
+          <t>15762A</t>
         </is>
       </c>
       <c r="B1148" s="5" t="inlineStr">
         <is>
-          <t>Rustilo 66 VCI, 18L AA</t>
+          <t>Rustilo 66 VCI, 200L AA</t>
         </is>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" s="4" t="inlineStr">
         <is>
-          <t>15762A</t>
+          <t>15761D</t>
         </is>
       </c>
       <c r="B1149" s="5" t="inlineStr">
         <is>
-          <t>Rustilo 66 VCI, 200L AA</t>
+          <t>Rustilo 66 VCI, 900L AA</t>
         </is>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" s="4" t="inlineStr">
         <is>
-          <t>15761D</t>
+          <t>154BDB</t>
         </is>
       </c>
       <c r="B1150" s="5" t="inlineStr">
         <is>
-          <t>Rustilo 66 VCI, 900L AA</t>
+          <t>Rustilo Aqua 2 FD, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" s="4" t="inlineStr">
         <is>
-          <t>154BDB</t>
+          <t>1574F3</t>
         </is>
       </c>
       <c r="B1151" s="5" t="inlineStr">
         <is>
-          <t>Rustilo Aqua 2 FD, 208L AA</t>
+          <t>Rustilo Aqua 21, 1000L AA</t>
         </is>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" s="4" t="inlineStr">
         <is>
-          <t>1574F3</t>
+          <t>1574EB</t>
         </is>
       </c>
       <c r="B1152" s="5" t="inlineStr">
         <is>
-          <t>Rustilo Aqua 21, 1000L AA</t>
+          <t>Rustilo Aqua 21, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" s="4" t="inlineStr">
         <is>
-          <t>1574EB</t>
+          <t>15D586</t>
         </is>
       </c>
       <c r="B1153" s="5" t="inlineStr">
         <is>
-          <t>Rustilo Aqua 21, 20L AA</t>
+          <t>Rustilo Aqua 30, 20K AA</t>
         </is>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" s="4" t="inlineStr">
         <is>
-          <t>15D586</t>
+          <t>157BA5</t>
         </is>
       </c>
       <c r="B1154" s="5" t="inlineStr">
         <is>
-          <t>Rustilo Aqua 30, 20K AA</t>
+          <t>Rustilo DW 100, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" s="4" t="inlineStr">
         <is>
-          <t>157BA5</t>
+          <t>15713F</t>
         </is>
       </c>
       <c r="B1155" s="5" t="inlineStr">
         <is>
-          <t>Rustilo DW 100, 20L AA</t>
+          <t>Rustilo DW 160 HF, 203L AA</t>
         </is>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" s="4" t="inlineStr">
         <is>
-          <t>15713F</t>
+          <t>156DEF</t>
         </is>
       </c>
       <c r="B1156" s="5" t="inlineStr">
         <is>
-          <t>Rustilo DW 160 HF, 203L AA</t>
+          <t>Rustilo DW 180 HF, 203L AA</t>
         </is>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" s="4" t="inlineStr">
         <is>
-          <t>156DEF</t>
+          <t>156DF0</t>
         </is>
       </c>
       <c r="B1157" s="5" t="inlineStr">
         <is>
-          <t>Rustilo DW 180 HF, 203L AA</t>
+          <t>Rustilo DW 180 HF, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" s="4" t="inlineStr">
         <is>
-          <t>156DF0</t>
+          <t>15CBD7</t>
         </is>
       </c>
       <c r="B1158" s="5" t="inlineStr">
         <is>
-          <t>Rustilo DW 180 HF, 20L AA</t>
+          <t>Rustilo DW 180 X, 203L AA N</t>
         </is>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" s="4" t="inlineStr">
         <is>
-          <t>15CBD7</t>
+          <t>15BEEB</t>
         </is>
       </c>
       <c r="B1159" s="5" t="inlineStr">
         <is>
-          <t>Rustilo DW 180 X, 203L AA N</t>
+          <t>Rustilo DW 210 X, 1000L AA</t>
         </is>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" s="4" t="inlineStr">
         <is>
-          <t>15BEEB</t>
+          <t>15BEEE</t>
         </is>
       </c>
       <c r="B1160" s="5" t="inlineStr">
         <is>
-          <t>Rustilo DW 210 X, 1000L AA</t>
+          <t>Rustilo DW 210 X, 203L AA</t>
         </is>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" s="4" t="inlineStr">
         <is>
-          <t>15BEEE</t>
+          <t>15BC78</t>
         </is>
       </c>
       <c r="B1161" s="5" t="inlineStr">
         <is>
-          <t>Rustilo DW 210 X, 203L AA</t>
+          <t>Rustilo DW 230 X, 203L AA</t>
         </is>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" s="4" t="inlineStr">
         <is>
-          <t>15BC78</t>
+          <t>15A491</t>
         </is>
       </c>
       <c r="B1162" s="5" t="inlineStr">
         <is>
-          <t>Rustilo DW 230 X, 203L AA</t>
+          <t>Rustilo DW 300 X, 203L N AA</t>
         </is>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" s="4" t="inlineStr">
         <is>
-          <t>15A491</t>
+          <t>15A48F</t>
         </is>
       </c>
       <c r="B1163" s="5" t="inlineStr">
         <is>
-          <t>Rustilo DW 300 X, 203L N AA</t>
+          <t>Rustilo DW 300 X, 20L N AA</t>
         </is>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" s="4" t="inlineStr">
         <is>
-          <t>15A48F</t>
+          <t>155F74</t>
         </is>
       </c>
       <c r="B1164" s="5" t="inlineStr">
         <is>
-          <t>Rustilo DW 300 X, 20L N AA</t>
+          <t>Rustilo DW 300, 203L AA</t>
         </is>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" s="4" t="inlineStr">
         <is>
-          <t>155F74</t>
+          <t>155F73</t>
         </is>
       </c>
       <c r="B1165" s="5" t="inlineStr">
         <is>
-          <t>Rustilo DW 300, 203L AA</t>
+          <t>Rustilo DW 300, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" s="4" t="inlineStr">
         <is>
-          <t>155F73</t>
+          <t>156DFA</t>
         </is>
       </c>
       <c r="B1166" s="5" t="inlineStr">
         <is>
-          <t>Rustilo DW 300, 20L AA</t>
+          <t>Rustilo DW 310 HF, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" s="4" t="inlineStr">
         <is>
-          <t>156DFA</t>
+          <t>1587B4</t>
         </is>
       </c>
       <c r="B1167" s="5" t="inlineStr">
         <is>
-          <t>Rustilo DW 310 HF, 20L AA</t>
+          <t>Rustilo DW 330, 203L AA</t>
         </is>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" s="4" t="inlineStr">
         <is>
-          <t>1587B4</t>
+          <t>1587B2</t>
         </is>
       </c>
       <c r="B1168" s="5" t="inlineStr">
         <is>
-          <t>Rustilo DW 330, 203L AA</t>
+          <t>Rustilo DW 330, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" s="4" t="inlineStr">
         <is>
-          <t>1587B2</t>
+          <t>15637E</t>
         </is>
       </c>
       <c r="B1169" s="5" t="inlineStr">
         <is>
-          <t>Rustilo DW 330, 20L AA</t>
+          <t>Rustilo DW 370, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" s="4" t="inlineStr">
         <is>
-          <t>15637E</t>
+          <t>15716C</t>
         </is>
       </c>
       <c r="B1170" s="5" t="inlineStr">
         <is>
-          <t>Rustilo DW 370, 20L AA</t>
+          <t>Rustilo DW 88 HF, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" s="4" t="inlineStr">
         <is>
-          <t>15716C</t>
+          <t>157AFA</t>
         </is>
       </c>
       <c r="B1171" s="5" t="inlineStr">
         <is>
-          <t>Rustilo DW 88 HF, 20L AA</t>
+          <t>Rustilo DWX 10, 203L AD</t>
         </is>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" s="4" t="inlineStr">
         <is>
-          <t>157AFA</t>
+          <t>157AFD</t>
         </is>
       </c>
       <c r="B1172" s="5" t="inlineStr">
         <is>
-          <t>Rustilo DWX 10, 203L AD</t>
+          <t>Rustilo DWX 10, 20L AD</t>
         </is>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" s="4" t="inlineStr">
         <is>
-          <t>157AFD</t>
+          <t>1558B4</t>
         </is>
       </c>
       <c r="B1173" s="5" t="inlineStr">
         <is>
-          <t>Rustilo DWX 10, 20L AD</t>
+          <t>Rustilo DWX 21, 203L AD</t>
         </is>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" s="4" t="inlineStr">
         <is>
-          <t>1558B4</t>
+          <t>1558B2</t>
         </is>
       </c>
       <c r="B1174" s="5" t="inlineStr">
         <is>
-          <t>Rustilo DWX 21, 203L AD</t>
+          <t>Rustilo DWX 21, 20L AD</t>
         </is>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" s="4" t="inlineStr">
         <is>
-          <t>1558B2</t>
+          <t>155FC2</t>
         </is>
       </c>
       <c r="B1175" s="5" t="inlineStr">
         <is>
-          <t>Rustilo DWX 21, 20L AD</t>
+          <t>Rustilo DWX 22, 203L AD</t>
         </is>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" s="4" t="inlineStr">
         <is>
-          <t>155FC2</t>
+          <t>15A019</t>
         </is>
       </c>
       <c r="B1176" s="5" t="inlineStr">
         <is>
-          <t>Rustilo DWX 22, 203L AD</t>
+          <t>Rustilo DWX 30, 203L AD</t>
         </is>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" s="4" t="inlineStr">
         <is>
-          <t>15A019</t>
+          <t>15A018</t>
         </is>
       </c>
       <c r="B1177" s="5" t="inlineStr">
         <is>
-          <t>Rustilo DWX 30, 203L AD</t>
+          <t>Rustilo DWX 30, 20L AD</t>
         </is>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" s="4" t="inlineStr">
         <is>
-          <t>15A018</t>
+          <t>155FCD</t>
         </is>
       </c>
       <c r="B1178" s="5" t="inlineStr">
         <is>
-          <t>Rustilo DWX 30, 20L AD</t>
+          <t>Rustilo DWX 32, 203L AD</t>
         </is>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" s="4" t="inlineStr">
         <is>
-          <t>155FCD</t>
+          <t>155FC8</t>
         </is>
       </c>
       <c r="B1179" s="5" t="inlineStr">
         <is>
-          <t>Rustilo DWX 32, 203L AD</t>
+          <t>Rustilo DWX 32, 20L AD</t>
         </is>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" s="4" t="inlineStr">
         <is>
-          <t>155FC8</t>
+          <t>15E20F</t>
         </is>
       </c>
       <c r="B1180" s="5" t="inlineStr">
         <is>
-          <t>Rustilo DWX 32, 20L AD</t>
+          <t>Rustilo WDP Spray, 12X.4L LS</t>
         </is>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" s="4" t="inlineStr">
         <is>
-          <t>15E20F</t>
+          <t>157A81</t>
         </is>
       </c>
       <c r="B1181" s="5" t="inlineStr">
         <is>
-          <t>Rustilo WDP Spray, 12X.4L LS</t>
+          <t>Spheerol AP 2, 18K E4</t>
         </is>
       </c>
     </row>
     <row r="1182">
       <c r="A1182" s="4" t="inlineStr">
         <is>
-          <t>157A81</t>
+          <t>14F57E</t>
         </is>
       </c>
       <c r="B1182" s="5" t="inlineStr">
         <is>
-          <t>Spheerol AP 2, 18K E4</t>
+          <t>Spheerol AP 3, 18K E4</t>
         </is>
       </c>
     </row>
     <row r="1183">
       <c r="A1183" s="4" t="inlineStr">
         <is>
-          <t>14F57E</t>
+          <t>1522F5</t>
         </is>
       </c>
       <c r="B1183" s="5" t="inlineStr">
         <is>
-          <t>Spheerol AP 3, 18K E4</t>
+          <t>Spheerol BNS 2, 15K E4</t>
         </is>
       </c>
     </row>
     <row r="1184">
       <c r="A1184" s="4" t="inlineStr">
         <is>
-          <t>1522F5</t>
+          <t>157BC3</t>
         </is>
       </c>
       <c r="B1184" s="5" t="inlineStr">
         <is>
-          <t>Spheerol BNS 2, 15K E4</t>
+          <t>Spheerol EPL 0, 12.5K E4</t>
         </is>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" s="4" t="inlineStr">
         <is>
-          <t>157BC3</t>
+          <t>15128B</t>
         </is>
       </c>
       <c r="B1185" s="5" t="inlineStr">
         <is>
-          <t>Spheerol EPL 0, 12.5K E4</t>
+          <t>Spheerol EPL 0, 18K E4</t>
         </is>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" s="4" t="inlineStr">
         <is>
-          <t>15128B</t>
+          <t>15A247</t>
         </is>
       </c>
       <c r="B1186" s="5" t="inlineStr">
         <is>
-          <t>Spheerol EPL 0, 18K E4</t>
+          <t>Spheerol EPL 00, 180K E4</t>
         </is>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" s="4" t="inlineStr">
         <is>
-          <t>15A247</t>
+          <t>14700C</t>
         </is>
       </c>
       <c r="B1187" s="5" t="inlineStr">
         <is>
-          <t>Spheerol EPL 00, 180K E4</t>
+          <t>Spheerol EPL 00, 18K E4</t>
         </is>
       </c>
     </row>
     <row r="1188">
       <c r="A1188" s="4" t="inlineStr">
         <is>
-          <t>14700C</t>
+          <t>15A15D</t>
         </is>
       </c>
       <c r="B1188" s="5" t="inlineStr">
         <is>
-          <t>Spheerol EPL 00, 18K E4</t>
+          <t>Spheerol EPL 1, 15K E4</t>
         </is>
       </c>
     </row>
     <row r="1189">
       <c r="A1189" s="4" t="inlineStr">
         <is>
-          <t>15A15D</t>
+          <t>148F1E</t>
         </is>
       </c>
       <c r="B1189" s="5" t="inlineStr">
         <is>
-          <t>Spheerol EPL 1, 15K E4</t>
+          <t>Spheerol EPL 1, 180K E4</t>
         </is>
       </c>
     </row>
     <row r="1190">
       <c r="A1190" s="4" t="inlineStr">
         <is>
-          <t>148F1E</t>
+          <t>139268</t>
         </is>
       </c>
       <c r="B1190" s="5" t="inlineStr">
         <is>
-          <t>Spheerol EPL 1, 180K E4</t>
+          <t>Spheerol EPL 1, 18K E4</t>
         </is>
       </c>
     </row>
     <row r="1191">
       <c r="A1191" s="4" t="inlineStr">
         <is>
-          <t>139268</t>
+          <t>159FE0</t>
         </is>
       </c>
       <c r="B1191" s="5" t="inlineStr">
         <is>
-          <t>Spheerol EPL 1, 18K E4</t>
+          <t>Spheerol EPL 2, 180K E4</t>
         </is>
       </c>
     </row>
     <row r="1192">
       <c r="A1192" s="4" t="inlineStr">
         <is>
-          <t>159FE0</t>
+          <t>1511A7</t>
         </is>
       </c>
       <c r="B1192" s="5" t="inlineStr">
         <is>
-          <t>Spheerol EPL 2, 180K E4</t>
+          <t>Spheerol EPL 2, 18K E4</t>
         </is>
       </c>
     </row>
     <row r="1193">
       <c r="A1193" s="4" t="inlineStr">
         <is>
-          <t>1511A7</t>
+          <t>138543</t>
         </is>
       </c>
       <c r="B1193" s="5" t="inlineStr">
         <is>
-          <t>Spheerol EPL 2, 18K E4</t>
+          <t>Spheerol EPL 2, 50K E4</t>
         </is>
       </c>
     </row>
     <row r="1194">
       <c r="A1194" s="4" t="inlineStr">
         <is>
-          <t>138543</t>
+          <t>15A33F</t>
         </is>
       </c>
       <c r="B1194" s="5" t="inlineStr">
         <is>
-          <t>Spheerol EPL 2, 50K E4</t>
+          <t>Spheerol EPL 3, 15K E4</t>
         </is>
       </c>
     </row>
     <row r="1195">
       <c r="A1195" s="4" t="inlineStr">
         <is>
-          <t>15A33F</t>
+          <t>15057D</t>
         </is>
       </c>
       <c r="B1195" s="5" t="inlineStr">
         <is>
-          <t>Spheerol EPL 3, 15K E4</t>
+          <t>Spheerol EPLX 200-2, 180K E4</t>
         </is>
       </c>
     </row>
     <row r="1196">
       <c r="A1196" s="4" t="inlineStr">
         <is>
-          <t>15057D</t>
+          <t>15057C</t>
         </is>
       </c>
       <c r="B1196" s="5" t="inlineStr">
         <is>
-          <t>Spheerol EPLX 200-2, 180K E4</t>
+          <t>Spheerol EPLX 200-2, 18K E4</t>
         </is>
       </c>
     </row>
     <row r="1197">
       <c r="A1197" s="4" t="inlineStr">
         <is>
-          <t>15057C</t>
+          <t>15B168</t>
         </is>
       </c>
       <c r="B1197" s="5" t="inlineStr">
         <is>
-          <t>Spheerol EPLX 200-2, 18K E4</t>
+          <t>Spheerol EPLX 200-2, 30X.4K E4</t>
         </is>
       </c>
     </row>
     <row r="1198">
       <c r="A1198" s="4" t="inlineStr">
         <is>
-          <t>15B168</t>
+          <t>156B61</t>
         </is>
       </c>
       <c r="B1198" s="5" t="inlineStr">
         <is>
-          <t>Spheerol EPLX 200-2, 30X.4K E4</t>
+          <t>Spheerol HTM 1, 180K E4</t>
         </is>
       </c>
     </row>
     <row r="1199">
       <c r="A1199" s="4" t="inlineStr">
         <is>
-          <t>156B61</t>
+          <t>156B5F</t>
         </is>
       </c>
       <c r="B1199" s="5" t="inlineStr">
         <is>
-          <t>Spheerol HTM 1, 180K E4</t>
+          <t>Spheerol HTM 1, 18K E4</t>
         </is>
       </c>
     </row>
     <row r="1200">
       <c r="A1200" s="4" t="inlineStr">
         <is>
-          <t>156B5F</t>
+          <t>14FB5D</t>
         </is>
       </c>
       <c r="B1200" s="5" t="inlineStr">
         <is>
-          <t>Spheerol HTM 1, 18K E4</t>
+          <t>Spheerol LC 2, 180K E4</t>
         </is>
       </c>
     </row>
     <row r="1201">
       <c r="A1201" s="4" t="inlineStr">
         <is>
-          <t>14FB5D</t>
+          <t>14F53A</t>
         </is>
       </c>
       <c r="B1201" s="5" t="inlineStr">
         <is>
-          <t>Spheerol LC 2, 180K E4</t>
+          <t>Spheerol LC 2, 18K E4</t>
         </is>
       </c>
     </row>
     <row r="1202">
       <c r="A1202" s="4" t="inlineStr">
         <is>
-          <t>14F53A</t>
+          <t>1501C6</t>
         </is>
       </c>
       <c r="B1202" s="5" t="inlineStr">
         <is>
-          <t>Spheerol LC 2, 18K E4</t>
+          <t>Spheerol LCX 222, 180K E4</t>
         </is>
       </c>
     </row>
     <row r="1203">
       <c r="A1203" s="4" t="inlineStr">
         <is>
-          <t>1501C6</t>
+          <t>1501C5</t>
         </is>
       </c>
       <c r="B1203" s="5" t="inlineStr">
         <is>
-          <t>Spheerol LCX 222, 180K E4</t>
+          <t>Spheerol LCX 222, 18K E4</t>
         </is>
       </c>
     </row>
     <row r="1204">
       <c r="A1204" s="4" t="inlineStr">
         <is>
-          <t>1501C5</t>
+          <t>15C57E</t>
         </is>
       </c>
       <c r="B1204" s="5" t="inlineStr">
         <is>
-          <t>Spheerol LCX 222, 18K E4</t>
+          <t>Spheerol LMM, 15K E4</t>
         </is>
       </c>
     </row>
     <row r="1205">
       <c r="A1205" s="4" t="inlineStr">
         <is>
-          <t>15C57E</t>
+          <t>15C580</t>
         </is>
       </c>
       <c r="B1205" s="5" t="inlineStr">
         <is>
-          <t>Spheerol LMM, 15K E4</t>
+          <t>Spheerol LMM, 180K E4</t>
         </is>
       </c>
     </row>
     <row r="1206">
       <c r="A1206" s="4" t="inlineStr">
         <is>
-          <t>15C580</t>
+          <t>15C57F</t>
         </is>
       </c>
       <c r="B1206" s="5" t="inlineStr">
         <is>
-          <t>Spheerol LMM, 180K E4</t>
+          <t>Spheerol LMM, 18K E4</t>
         </is>
       </c>
     </row>
     <row r="1207">
       <c r="A1207" s="4" t="inlineStr">
         <is>
-          <t>15C57F</t>
+          <t>15C582</t>
         </is>
       </c>
       <c r="B1207" s="5" t="inlineStr">
         <is>
-          <t>Spheerol LMM, 18K E4</t>
+          <t>Spheerol LMM, 30X.4K E4</t>
         </is>
       </c>
     </row>
     <row r="1208">
       <c r="A1208" s="4" t="inlineStr">
         <is>
-          <t>15C582</t>
+          <t>15B178</t>
         </is>
       </c>
       <c r="B1208" s="5" t="inlineStr">
         <is>
-          <t>Spheerol LMM, 30X.4K E4</t>
+          <t>Spheerol SX 2, 12X.4K E4</t>
         </is>
       </c>
     </row>
     <row r="1209">
       <c r="A1209" s="4" t="inlineStr">
         <is>
-          <t>15B178</t>
+          <t>1511B3</t>
         </is>
       </c>
       <c r="B1209" s="5" t="inlineStr">
         <is>
-          <t>Spheerol SX 2, 12X.4K E4</t>
+          <t>Spheerol SX 2, 180K E4</t>
         </is>
       </c>
     </row>
     <row r="1210">
       <c r="A1210" s="4" t="inlineStr">
         <is>
-          <t>1511B3</t>
+          <t>14E2C1</t>
         </is>
       </c>
       <c r="B1210" s="5" t="inlineStr">
         <is>
-          <t>Spheerol SX 2, 180K E4</t>
+          <t>Spheerol SX 2, 18K E4</t>
         </is>
       </c>
     </row>
     <row r="1211">
       <c r="A1211" s="4" t="inlineStr">
         <is>
-          <t>14E2C1</t>
+          <t>15E5E5</t>
         </is>
       </c>
       <c r="B1211" s="5" t="inlineStr">
         <is>
-          <t>Spheerol SX 2, 18K E4</t>
+          <t>Spheerol SY 1002, 20K 1E</t>
         </is>
       </c>
     </row>
     <row r="1212">
       <c r="A1212" s="4" t="inlineStr">
         <is>
-          <t>15E5E5</t>
+          <t>1563CF</t>
         </is>
       </c>
       <c r="B1212" s="5" t="inlineStr">
         <is>
-          <t>Spheerol SY 1002, 20K 1E</t>
+          <t>Spheerol SY 1501, 165K E4</t>
         </is>
       </c>
     </row>
     <row r="1213">
       <c r="A1213" s="4" t="inlineStr">
         <is>
-          <t>1563CF</t>
+          <t>1563DA</t>
         </is>
       </c>
       <c r="B1213" s="5" t="inlineStr">
         <is>
-          <t>Spheerol SY 1501, 165K E4</t>
+          <t>Spheerol SY 1501, 20K E4</t>
         </is>
       </c>
     </row>
     <row r="1214">
       <c r="A1214" s="4" t="inlineStr">
         <is>
-          <t>1563DA</t>
+          <t>14FB29</t>
         </is>
       </c>
       <c r="B1214" s="5" t="inlineStr">
         <is>
-          <t>Spheerol SY 1501, 20K E4</t>
+          <t>Spheerol SY 2202, 20K E4</t>
         </is>
       </c>
     </row>
     <row r="1215">
       <c r="A1215" s="4" t="inlineStr">
         <is>
-          <t>14FB29</t>
+          <t>15011D</t>
         </is>
       </c>
       <c r="B1215" s="5" t="inlineStr">
         <is>
-          <t>Spheerol SY 2202, 20K E4</t>
+          <t>Spheerol SY 4601, 165K E4</t>
         </is>
       </c>
     </row>
     <row r="1216">
       <c r="A1216" s="4" t="inlineStr">
         <is>
-          <t>15011D</t>
+          <t>15011E</t>
         </is>
       </c>
       <c r="B1216" s="5" t="inlineStr">
         <is>
-          <t>Spheerol SY 4601, 165K E4</t>
+          <t>Spheerol SY 4601, 18K E4</t>
         </is>
       </c>
     </row>
     <row r="1217">
       <c r="A1217" s="4" t="inlineStr">
         <is>
-          <t>15011E</t>
+          <t>156C2C</t>
         </is>
       </c>
       <c r="B1217" s="5" t="inlineStr">
         <is>
-          <t>Spheerol SY 4601, 18K E4</t>
+          <t>Spheerol SY-HT 2, 20K E4</t>
         </is>
       </c>
     </row>
     <row r="1218">
       <c r="A1218" s="4" t="inlineStr">
         <is>
-          <t>156C2C</t>
+          <t>1561DF</t>
         </is>
       </c>
       <c r="B1218" s="5" t="inlineStr">
         <is>
-          <t>Spheerol SY-HT 2, 20K E4</t>
+          <t>Spheerol TN, 50K N E4</t>
         </is>
       </c>
     </row>
     <row r="1219">
       <c r="A1219" s="4" t="inlineStr">
         <is>
-          <t>1561DF</t>
+          <t>155A79</t>
         </is>
       </c>
       <c r="B1219" s="5" t="inlineStr">
         <is>
-          <t>Spheerol TN, 50K N E4</t>
+          <t>Surfactant S 625, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1220">
       <c r="A1220" s="4" t="inlineStr">
         <is>
-          <t>155A79</t>
+          <t>154D9D</t>
         </is>
       </c>
       <c r="B1220" s="5" t="inlineStr">
         <is>
-          <t>Surfactant S 625, 20L E4</t>
+          <t>Syntilo 2000, 1000L N E4</t>
         </is>
       </c>
     </row>
     <row r="1221">
       <c r="A1221" s="4" t="inlineStr">
         <is>
-          <t>154D9D</t>
+          <t>154DA0</t>
         </is>
       </c>
       <c r="B1221" s="5" t="inlineStr">
         <is>
-          <t>Syntilo 2000, 1000L N E4</t>
+          <t>Syntilo 2000, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1222">
       <c r="A1222" s="4" t="inlineStr">
         <is>
-          <t>154DA0</t>
+          <t>154D9E</t>
         </is>
       </c>
       <c r="B1222" s="5" t="inlineStr">
         <is>
-          <t>Syntilo 2000, 208L E4</t>
+          <t>Syntilo 2000, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1223">
       <c r="A1223" s="4" t="inlineStr">
         <is>
-          <t>154D9E</t>
+          <t>154B19</t>
         </is>
       </c>
       <c r="B1223" s="5" t="inlineStr">
         <is>
-          <t>Syntilo 2000, 20L E4</t>
+          <t>Syntilo 75 EF, 1000L AA</t>
         </is>
       </c>
     </row>
     <row r="1224">
       <c r="A1224" s="4" t="inlineStr">
         <is>
-          <t>154B19</t>
+          <t>154B16</t>
         </is>
       </c>
       <c r="B1224" s="5" t="inlineStr">
         <is>
-          <t>Syntilo 75 EF, 1000L AA</t>
+          <t>Syntilo 75 EF, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1225">
       <c r="A1225" s="4" t="inlineStr">
         <is>
-          <t>154B16</t>
+          <t>154B14</t>
         </is>
       </c>
       <c r="B1225" s="5" t="inlineStr">
         <is>
-          <t>Syntilo 75 EF, 208L AA</t>
+          <t>Syntilo 75 EF, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1226">
       <c r="A1226" s="4" t="inlineStr">
         <is>
-          <t>154B14</t>
+          <t>15A50B</t>
         </is>
       </c>
       <c r="B1226" s="5" t="inlineStr">
         <is>
-          <t>Syntilo 75 EF, 20L AA</t>
+          <t>Syntilo 81 BF, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1227">
       <c r="A1227" s="4" t="inlineStr">
         <is>
-          <t>15A50B</t>
+          <t>15A509</t>
         </is>
       </c>
       <c r="B1227" s="5" t="inlineStr">
         <is>
-          <t>Syntilo 81 BF, 208L AA</t>
+          <t>Syntilo 81 BF, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1228">
       <c r="A1228" s="4" t="inlineStr">
         <is>
-          <t>15A509</t>
+          <t>1550BB</t>
         </is>
       </c>
       <c r="B1228" s="5" t="inlineStr">
         <is>
-          <t>Syntilo 81 BF, 20L AA</t>
+          <t>Syntilo 81 E, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1229">
       <c r="A1229" s="4" t="inlineStr">
         <is>
-          <t>1550BB</t>
+          <t>1550BA</t>
         </is>
       </c>
       <c r="B1229" s="5" t="inlineStr">
         <is>
-          <t>Syntilo 81 E, 208L E4</t>
+          <t>Syntilo 81 E, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1230">
       <c r="A1230" s="4" t="inlineStr">
         <is>
-          <t>1550BA</t>
+          <t>155AA5</t>
         </is>
       </c>
       <c r="B1230" s="5" t="inlineStr">
         <is>
-          <t>Syntilo 81 E, 20L E4</t>
+          <t>Syntilo 9913, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1231">
       <c r="A1231" s="4" t="inlineStr">
         <is>
-          <t>155AA5</t>
+          <t>155AA1</t>
         </is>
       </c>
       <c r="B1231" s="5" t="inlineStr">
         <is>
-          <t>Syntilo 9913, 208L AA</t>
+          <t>Syntilo 9913, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1232">
       <c r="A1232" s="4" t="inlineStr">
         <is>
-          <t>155AA1</t>
+          <t>154AFA</t>
         </is>
       </c>
       <c r="B1232" s="5" t="inlineStr">
         <is>
-          <t>Syntilo 9913, 20L AA</t>
+          <t>Syntilo 9931 BF, 1000L AA</t>
         </is>
       </c>
     </row>
     <row r="1233">
       <c r="A1233" s="4" t="inlineStr">
         <is>
-          <t>154AFA</t>
+          <t>154AFD</t>
         </is>
       </c>
       <c r="B1233" s="5" t="inlineStr">
         <is>
-          <t>Syntilo 9931 BF, 1000L AA</t>
+          <t>Syntilo 9931 BF, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1234">
       <c r="A1234" s="4" t="inlineStr">
         <is>
-          <t>154AFD</t>
+          <t>154B00</t>
         </is>
       </c>
       <c r="B1234" s="5" t="inlineStr">
         <is>
-          <t>Syntilo 9931 BF, 208L AA</t>
+          <t>Syntilo 9931 BF, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1235">
       <c r="A1235" s="4" t="inlineStr">
         <is>
-          <t>154B00</t>
+          <t>14A2A7</t>
         </is>
       </c>
       <c r="B1235" s="5" t="inlineStr">
         <is>
-          <t>Syntilo 9931 BF, 20L AA</t>
+          <t>Syntilo 9954, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1236">
       <c r="A1236" s="4" t="inlineStr">
         <is>
-          <t>14A2A7</t>
+          <t>14A2A6</t>
         </is>
       </c>
       <c r="B1236" s="5" t="inlineStr">
         <is>
-          <t>Syntilo 9954, 208L E4</t>
+          <t>Syntilo 9954, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1237">
       <c r="A1237" s="4" t="inlineStr">
         <is>
-          <t>14A2A6</t>
+          <t>155C1C</t>
         </is>
       </c>
       <c r="B1237" s="5" t="inlineStr">
         <is>
-          <t>Syntilo 9954, 20L E4</t>
+          <t>Syntilo 9974 BF, 1000L AA</t>
         </is>
       </c>
     </row>
     <row r="1238">
       <c r="A1238" s="4" t="inlineStr">
         <is>
-          <t>155C1C</t>
+          <t>155C1A</t>
         </is>
       </c>
       <c r="B1238" s="5" t="inlineStr">
         <is>
-          <t>Syntilo 9974 BF, 1000L AA</t>
+          <t>Syntilo 9974 BF, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1239">
       <c r="A1239" s="4" t="inlineStr">
         <is>
-          <t>155C1A</t>
+          <t>1553B9</t>
         </is>
       </c>
       <c r="B1239" s="5" t="inlineStr">
         <is>
-          <t>Syntilo 9974 BF, 208L AA</t>
+          <t>Syntilo CR 4, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1240">
       <c r="A1240" s="4" t="inlineStr">
         <is>
-          <t>1553B9</t>
+          <t>1553B6</t>
         </is>
       </c>
       <c r="B1240" s="5" t="inlineStr">
         <is>
-          <t>Syntilo CR 4, 208L AA</t>
+          <t>Syntilo CR 4, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1241">
       <c r="A1241" s="4" t="inlineStr">
         <is>
-          <t>1553B6</t>
+          <t>14FB34</t>
         </is>
       </c>
       <c r="B1241" s="5" t="inlineStr">
         <is>
-          <t>Syntilo CR 4, 20L AA</t>
+          <t>Syntilo MR 81 BF, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1242">
       <c r="A1242" s="4" t="inlineStr">
         <is>
-          <t>14FB34</t>
+          <t>14FB35</t>
         </is>
       </c>
       <c r="B1242" s="5" t="inlineStr">
         <is>
-          <t>Syntilo MR 81 BF, 208L E4</t>
+          <t>Syntilo MR 81 BF, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1243">
       <c r="A1243" s="4" t="inlineStr">
         <is>
-          <t>14FB35</t>
+          <t>15D8F8</t>
         </is>
       </c>
       <c r="B1243" s="5" t="inlineStr">
         <is>
-          <t>Syntilo MR 81 BF, 20L E4</t>
+          <t>Syntilo MR 9974 BF, 1000L AA</t>
         </is>
       </c>
     </row>
     <row r="1244">
       <c r="A1244" s="4" t="inlineStr">
         <is>
-          <t>15D8F8</t>
+          <t>15D8F6</t>
         </is>
       </c>
       <c r="B1244" s="5" t="inlineStr">
         <is>
-          <t>Syntilo MR 9974 BF, 1000L AA</t>
+          <t>Syntilo MR 9974 BF, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1245">
       <c r="A1245" s="4" t="inlineStr">
         <is>
-          <t>15D8F6</t>
+          <t>15D8F7</t>
         </is>
       </c>
       <c r="B1245" s="5" t="inlineStr">
         <is>
-          <t>Syntilo MR 9974 BF, 208L AA</t>
+          <t>Syntilo MR 9974 BF, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1246">
       <c r="A1246" s="4" t="inlineStr">
         <is>
-          <t>15D8F7</t>
+          <t>154C51</t>
         </is>
       </c>
       <c r="B1246" s="5" t="inlineStr">
         <is>
-          <t>Syntilo MR 9974 BF, 20L AA</t>
+          <t>Techniclean 227, 1000L AA</t>
         </is>
       </c>
     </row>
     <row r="1247">
       <c r="A1247" s="4" t="inlineStr">
         <is>
-          <t>154C51</t>
+          <t>154C52</t>
         </is>
       </c>
       <c r="B1247" s="5" t="inlineStr">
         <is>
-          <t>Techniclean 227, 1000L AA</t>
+          <t>Techniclean 227, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1248">
       <c r="A1248" s="4" t="inlineStr">
         <is>
-          <t>154C52</t>
+          <t>154C53</t>
         </is>
       </c>
       <c r="B1248" s="5" t="inlineStr">
         <is>
-          <t>Techniclean 227, 208L AA</t>
+          <t>Techniclean 227, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1249">
       <c r="A1249" s="4" t="inlineStr">
         <is>
-          <t>154C53</t>
+          <t>15CF22</t>
         </is>
       </c>
       <c r="B1249" s="5" t="inlineStr">
         <is>
-          <t>Techniclean 227, 20L AA</t>
+          <t>Techniclean 45 XBC, 1000L AA</t>
         </is>
       </c>
     </row>
     <row r="1250">
       <c r="A1250" s="4" t="inlineStr">
         <is>
-          <t>15CF22</t>
+          <t>15D56F</t>
         </is>
       </c>
       <c r="B1250" s="5" t="inlineStr">
         <is>
-          <t>Techniclean 45 XBC, 1000L AA</t>
+          <t>Techniclean 45 XBC, 215L AA</t>
         </is>
       </c>
     </row>
     <row r="1251">
       <c r="A1251" s="4" t="inlineStr">
         <is>
-          <t>15D56F</t>
+          <t>15C138</t>
         </is>
       </c>
       <c r="B1251" s="5" t="inlineStr">
         <is>
-          <t>Techniclean 45 XBC, 215L AA</t>
+          <t>Techniclean 80 XBC, 1000L AA</t>
         </is>
       </c>
     </row>
     <row r="1252">
       <c r="A1252" s="4" t="inlineStr">
         <is>
-          <t>15C138</t>
+          <t>15C137</t>
         </is>
       </c>
       <c r="B1252" s="5" t="inlineStr">
         <is>
-          <t>Techniclean 80 XBC, 1000L AA</t>
+          <t>Techniclean 80 XBC, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1253">
       <c r="A1253" s="4" t="inlineStr">
         <is>
-          <t>15C137</t>
+          <t>15C136</t>
         </is>
       </c>
       <c r="B1253" s="5" t="inlineStr">
         <is>
-          <t>Techniclean 80 XBC, 208L AA</t>
+          <t>Techniclean 80 XBC, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1254">
       <c r="A1254" s="4" t="inlineStr">
         <is>
-          <t>15C136</t>
+          <t>155A15</t>
         </is>
       </c>
       <c r="B1254" s="5" t="inlineStr">
         <is>
-          <t>Techniclean 80 XBC, 20L AA</t>
+          <t>Techniclean 8580, 1000L AA</t>
         </is>
       </c>
     </row>
     <row r="1255">
       <c r="A1255" s="4" t="inlineStr">
         <is>
-          <t>155A15</t>
+          <t>155A16</t>
         </is>
       </c>
       <c r="B1255" s="5" t="inlineStr">
         <is>
-          <t>Techniclean 8580, 1000L AA</t>
+          <t>Techniclean 8580, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1256">
       <c r="A1256" s="4" t="inlineStr">
         <is>
-          <t>155A16</t>
+          <t>155A17</t>
         </is>
       </c>
       <c r="B1256" s="5" t="inlineStr">
         <is>
-          <t>Techniclean 8580, 208L AA</t>
+          <t>Techniclean 8580, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1257">
       <c r="A1257" s="4" t="inlineStr">
         <is>
-          <t>155A17</t>
+          <t>15C0F6</t>
         </is>
       </c>
       <c r="B1257" s="5" t="inlineStr">
         <is>
-          <t>Techniclean 8580, 20L AA</t>
+          <t>Techniclean 90 XBC, 1000L AA</t>
         </is>
       </c>
     </row>
     <row r="1258">
       <c r="A1258" s="4" t="inlineStr">
         <is>
-          <t>15C0F6</t>
+          <t>15C0F5</t>
         </is>
       </c>
       <c r="B1258" s="5" t="inlineStr">
         <is>
-          <t>Techniclean 90 XBC, 1000L AA</t>
+          <t>Techniclean 90 XBC, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1259">
       <c r="A1259" s="4" t="inlineStr">
         <is>
-          <t>15C0F5</t>
+          <t>15C0F4</t>
         </is>
       </c>
       <c r="B1259" s="5" t="inlineStr">
         <is>
-          <t>Techniclean 90 XBC, 208L AA</t>
+          <t>Techniclean 90 XBC, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1260">
       <c r="A1260" s="4" t="inlineStr">
         <is>
-          <t>15C0F4</t>
+          <t>15465E</t>
         </is>
       </c>
       <c r="B1260" s="5" t="inlineStr">
         <is>
-          <t>Techniclean 90 XBC, 20L AA</t>
+          <t>Techniclean AS 105, 1000L AA</t>
         </is>
       </c>
     </row>
     <row r="1261">
       <c r="A1261" s="4" t="inlineStr">
         <is>
-          <t>15465E</t>
+          <t>15464D</t>
         </is>
       </c>
       <c r="B1261" s="5" t="inlineStr">
         <is>
-          <t>Techniclean AS 105, 1000L AA</t>
+          <t>Techniclean AS 105, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1262">
       <c r="A1262" s="4" t="inlineStr">
         <is>
-          <t>15464D</t>
+          <t>154BA2</t>
         </is>
       </c>
       <c r="B1262" s="5" t="inlineStr">
         <is>
-          <t>Techniclean AS 105, 208L AA</t>
+          <t>Techniclean AS 58, 203L AA</t>
         </is>
       </c>
     </row>
     <row r="1263">
       <c r="A1263" s="4" t="inlineStr">
         <is>
-          <t>154BA2</t>
+          <t>154BA0</t>
         </is>
       </c>
       <c r="B1263" s="5" t="inlineStr">
         <is>
-          <t>Techniclean AS 58, 203L AA</t>
+          <t>Techniclean AS 58, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1264">
       <c r="A1264" s="4" t="inlineStr">
         <is>
-          <t>154BA0</t>
+          <t>15466A</t>
         </is>
       </c>
       <c r="B1264" s="5" t="inlineStr">
         <is>
-          <t>Techniclean AS 58, 20L AA</t>
+          <t>Techniclean AS 62, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1265">
       <c r="A1265" s="4" t="inlineStr">
         <is>
-          <t>15466A</t>
+          <t>15466B</t>
         </is>
       </c>
       <c r="B1265" s="5" t="inlineStr">
         <is>
-          <t>Techniclean AS 62, 208L AA</t>
+          <t>Techniclean AS 62, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1266">
       <c r="A1266" s="4" t="inlineStr">
         <is>
-          <t>15466B</t>
+          <t>15AB61</t>
         </is>
       </c>
       <c r="B1266" s="5" t="inlineStr">
         <is>
-          <t>Techniclean AS 62, 20L AA</t>
+          <t>Techniclean BS 1, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1267">
       <c r="A1267" s="4" t="inlineStr">
         <is>
-          <t>15AB61</t>
+          <t>155AF8</t>
         </is>
       </c>
       <c r="B1267" s="5" t="inlineStr">
         <is>
-          <t>Techniclean BS 1, 20L AA</t>
+          <t>Techniclean D 890, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1268">
       <c r="A1268" s="4" t="inlineStr">
         <is>
-          <t>155AF8</t>
+          <t>15504B</t>
         </is>
       </c>
       <c r="B1268" s="5" t="inlineStr">
         <is>
-          <t>Techniclean D 890, 20L AA</t>
+          <t>Techniclean HP, 1000L AA</t>
         </is>
       </c>
     </row>
     <row r="1269">
       <c r="A1269" s="4" t="inlineStr">
         <is>
-          <t>15504B</t>
+          <t>15505C</t>
         </is>
       </c>
       <c r="B1269" s="5" t="inlineStr">
         <is>
-          <t>Techniclean HP, 1000L AA</t>
+          <t>Techniclean HP, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1270">
       <c r="A1270" s="4" t="inlineStr">
         <is>
-          <t>15505C</t>
+          <t>15504E</t>
         </is>
       </c>
       <c r="B1270" s="5" t="inlineStr">
         <is>
-          <t>Techniclean HP, 208L AA</t>
+          <t>Techniclean HP, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1271">
       <c r="A1271" s="4" t="inlineStr">
         <is>
-          <t>15504E</t>
+          <t>15E70B</t>
         </is>
       </c>
       <c r="B1271" s="5" t="inlineStr">
         <is>
-          <t>Techniclean HP, 20L AA</t>
+          <t>Techniclean IPA 100 WFS, 1L Q6</t>
         </is>
       </c>
     </row>
     <row r="1272">
       <c r="A1272" s="4" t="inlineStr">
         <is>
-          <t>15E70B</t>
+          <t>15673F</t>
         </is>
       </c>
       <c r="B1272" s="5" t="inlineStr">
         <is>
-          <t>Techniclean IPA 100 WFS, 1L Q6</t>
+          <t>Techniclean MP Flex, 1000L AA</t>
         </is>
       </c>
     </row>
     <row r="1273">
       <c r="A1273" s="4" t="inlineStr">
         <is>
-          <t>15673F</t>
+          <t>15672F</t>
         </is>
       </c>
       <c r="B1273" s="5" t="inlineStr">
         <is>
-          <t>Techniclean MP Flex, 1000L AA</t>
+          <t>Techniclean MP Flex, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1274">
       <c r="A1274" s="4" t="inlineStr">
         <is>
-          <t>15672F</t>
+          <t>15673D</t>
         </is>
       </c>
       <c r="B1274" s="5" t="inlineStr">
         <is>
-          <t>Techniclean MP Flex, 20L AA</t>
+          <t>Techniclean MP Flex, 215L AA</t>
         </is>
       </c>
     </row>
     <row r="1275">
       <c r="A1275" s="4" t="inlineStr">
         <is>
-          <t>15673D</t>
+          <t>155A67</t>
         </is>
       </c>
       <c r="B1275" s="5" t="inlineStr">
         <is>
-          <t>Techniclean MP Flex, 215L AA</t>
+          <t>Techniclean MP, 215L AA</t>
         </is>
       </c>
     </row>
     <row r="1276">
       <c r="A1276" s="4" t="inlineStr">
         <is>
-          <t>155A67</t>
+          <t>159EED</t>
         </is>
       </c>
       <c r="B1276" s="5" t="inlineStr">
         <is>
-          <t>Techniclean MP, 215L AA</t>
+          <t>Techniclean MTC 43, 208L N AA</t>
         </is>
       </c>
     </row>
     <row r="1277">
       <c r="A1277" s="4" t="inlineStr">
         <is>
-          <t>159EED</t>
+          <t>159EEB</t>
         </is>
       </c>
       <c r="B1277" s="5" t="inlineStr">
         <is>
-          <t>Techniclean MTC 43, 208L N AA</t>
+          <t>Techniclean MTC 43, 20L N AA</t>
         </is>
       </c>
     </row>
     <row r="1278">
       <c r="A1278" s="4" t="inlineStr">
         <is>
-          <t>159EEB</t>
+          <t>1545CC</t>
         </is>
       </c>
       <c r="B1278" s="5" t="inlineStr">
         <is>
-          <t>Techniclean MTC 43, 20L N AA</t>
+          <t>Techniclean OX 1 WDL, 1L Q6</t>
         </is>
       </c>
     </row>
     <row r="1279">
       <c r="A1279" s="4" t="inlineStr">
         <is>
-          <t>1545CC</t>
+          <t>15E2C6</t>
         </is>
       </c>
       <c r="B1279" s="5" t="inlineStr">
         <is>
-          <t>Techniclean OX 1 WDL, 1L Q6</t>
+          <t>Techniclean OX 1, .25L AK</t>
         </is>
       </c>
     </row>
     <row r="1280">
       <c r="A1280" s="4" t="inlineStr">
         <is>
-          <t>15E2C6</t>
+          <t>157BFA</t>
         </is>
       </c>
       <c r="B1280" s="5" t="inlineStr">
         <is>
-          <t>Techniclean OX 1, .25L AK</t>
+          <t>Techniclean S 20, 1000L AA</t>
         </is>
       </c>
     </row>
     <row r="1281">
       <c r="A1281" s="4" t="inlineStr">
         <is>
-          <t>157BFA</t>
+          <t>157BFE</t>
         </is>
       </c>
       <c r="B1281" s="5" t="inlineStr">
         <is>
-          <t>Techniclean S 20, 1000L AA</t>
+          <t>Techniclean S 20, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1282">
       <c r="A1282" s="4" t="inlineStr">
         <is>
-          <t>157BFE</t>
+          <t>1564AD</t>
         </is>
       </c>
       <c r="B1282" s="5" t="inlineStr">
         <is>
-          <t>Techniclean S 20, 208L AA</t>
+          <t>Techniclean S 30, 1000L AA</t>
         </is>
       </c>
     </row>
     <row r="1283">
       <c r="A1283" s="4" t="inlineStr">
         <is>
-          <t>1564AD</t>
+          <t>1564AF</t>
         </is>
       </c>
       <c r="B1283" s="5" t="inlineStr">
         <is>
-          <t>Techniclean S 30, 1000L AA</t>
+          <t>Techniclean S 30, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1284">
       <c r="A1284" s="4" t="inlineStr">
         <is>
-          <t>1564AF</t>
+          <t>15538B</t>
         </is>
       </c>
       <c r="B1284" s="5" t="inlineStr">
         <is>
-          <t>Techniclean S 30, 208L AA</t>
+          <t>Techniclean S 581, 1000L AA</t>
         </is>
       </c>
     </row>
     <row r="1285">
       <c r="A1285" s="4" t="inlineStr">
         <is>
-          <t>15538B</t>
+          <t>15538C</t>
         </is>
       </c>
       <c r="B1285" s="5" t="inlineStr">
         <is>
-          <t>Techniclean S 581, 1000L AA</t>
+          <t>Techniclean S 581, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1286">
       <c r="A1286" s="4" t="inlineStr">
         <is>
-          <t>15538C</t>
+          <t>15539A</t>
         </is>
       </c>
       <c r="B1286" s="5" t="inlineStr">
         <is>
-          <t>Techniclean S 581, 208L AA</t>
+          <t>Techniclean S 581, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1287">
       <c r="A1287" s="4" t="inlineStr">
         <is>
-          <t>15539A</t>
+          <t>155AB4</t>
         </is>
       </c>
       <c r="B1287" s="5" t="inlineStr">
         <is>
-          <t>Techniclean S 581, 20L AA</t>
+          <t>Techniclean S 9, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1288">
       <c r="A1288" s="4" t="inlineStr">
         <is>
-          <t>155AB4</t>
+          <t>155AB2</t>
         </is>
       </c>
       <c r="B1288" s="5" t="inlineStr">
         <is>
-          <t>Techniclean S 9, 208L AA</t>
+          <t>Techniclean S 9, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1289">
       <c r="A1289" s="4" t="inlineStr">
         <is>
-          <t>155AB2</t>
+          <t>155AC8</t>
         </is>
       </c>
       <c r="B1289" s="5" t="inlineStr">
         <is>
-          <t>Techniclean S 9, 20L AA</t>
+          <t>Techniclean S Extra FF, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1290">
       <c r="A1290" s="4" t="inlineStr">
         <is>
-          <t>155AC8</t>
+          <t>15AE4C</t>
         </is>
       </c>
       <c r="B1290" s="5" t="inlineStr">
         <is>
-          <t>Techniclean S Extra FF, 208L AA</t>
+          <t>Techniclean SC 170, 208L HA</t>
         </is>
       </c>
     </row>
     <row r="1291">
       <c r="A1291" s="4" t="inlineStr">
         <is>
-          <t>15AE4C</t>
+          <t>15AE4B</t>
         </is>
       </c>
       <c r="B1291" s="5" t="inlineStr">
         <is>
-          <t>Techniclean SC 170, 208L HA</t>
+          <t>Techniclean SC 170, 20L HA</t>
         </is>
       </c>
     </row>
     <row r="1292">
       <c r="A1292" s="4" t="inlineStr">
         <is>
-          <t>15AE4B</t>
+          <t>15833B</t>
         </is>
       </c>
       <c r="B1292" s="5" t="inlineStr">
         <is>
-          <t>Techniclean SC 170, 20L HA</t>
+          <t>Techniclean SC 320, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1293">
       <c r="A1293" s="4" t="inlineStr">
         <is>
-          <t>15833B</t>
+          <t>155A84</t>
         </is>
       </c>
       <c r="B1293" s="5" t="inlineStr">
         <is>
-          <t>Techniclean SC 320, 20L E4</t>
+          <t>Techniclean SF, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1294">
       <c r="A1294" s="4" t="inlineStr">
         <is>
-          <t>155A84</t>
+          <t>15C2A6</t>
         </is>
       </c>
       <c r="B1294" s="5" t="inlineStr">
         <is>
-          <t>Techniclean SF, 20L AA</t>
+          <t>Techniclean S-Premium, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1295">
       <c r="A1295" s="4" t="inlineStr">
         <is>
-          <t>15C2A6</t>
+          <t>15C2A8</t>
         </is>
       </c>
       <c r="B1295" s="5" t="inlineStr">
         <is>
-          <t>Techniclean S-Premium, 20L AA</t>
+          <t>Techniclean S-Premium, 215L AA</t>
         </is>
       </c>
     </row>
     <row r="1296">
       <c r="A1296" s="4" t="inlineStr">
         <is>
-          <t>15C2A8</t>
+          <t>15E0A0</t>
         </is>
       </c>
       <c r="B1296" s="5" t="inlineStr">
         <is>
-          <t>Techniclean S-Premium, 215L AA</t>
+          <t>Techniclean S-RP, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1297">
       <c r="A1297" s="4" t="inlineStr">
         <is>
-          <t>15E0A0</t>
+          <t>15E09F</t>
         </is>
       </c>
       <c r="B1297" s="5" t="inlineStr">
         <is>
-          <t>Techniclean S-RP, 208L AA</t>
+          <t>Techniclean S-RP, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1298">
       <c r="A1298" s="4" t="inlineStr">
         <is>
-          <t>15E09F</t>
+          <t>15722C</t>
         </is>
       </c>
       <c r="B1298" s="5" t="inlineStr">
         <is>
-          <t>Techniclean S-RP, 20L AA</t>
+          <t>Techniclean Tablefit WDL, 1.47L Q6</t>
         </is>
       </c>
     </row>
     <row r="1299">
       <c r="A1299" s="4" t="inlineStr">
         <is>
-          <t>15722C</t>
+          <t>1564F0</t>
         </is>
       </c>
       <c r="B1299" s="5" t="inlineStr">
         <is>
-          <t>Techniclean Tablefit WDL, 1.47L Q6</t>
+          <t>Techniclean XHD, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1300">
       <c r="A1300" s="4" t="inlineStr">
         <is>
-          <t>1564F0</t>
+          <t>15647E</t>
         </is>
       </c>
       <c r="B1300" s="5" t="inlineStr">
         <is>
-          <t>Techniclean XHD, 20L AA</t>
+          <t>Tribol 1060/220, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1301">
       <c r="A1301" s="4" t="inlineStr">
         <is>
-          <t>15647E</t>
+          <t>154A6A</t>
         </is>
       </c>
       <c r="B1301" s="5" t="inlineStr">
         <is>
-          <t>Tribol 1060/220, 20L E4</t>
+          <t>Tribol 1899, 5L E4</t>
         </is>
       </c>
     </row>
     <row r="1302">
       <c r="A1302" s="4" t="inlineStr">
         <is>
-          <t>154A6A</t>
+          <t>15BA37</t>
         </is>
       </c>
       <c r="B1302" s="5" t="inlineStr">
         <is>
-          <t>Tribol 1899, 5L E4</t>
+          <t>Tribol CH 1330, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1303">
       <c r="A1303" s="4" t="inlineStr">
         <is>
-          <t>15BA37</t>
+          <t>15BA36</t>
         </is>
       </c>
       <c r="B1303" s="5" t="inlineStr">
         <is>
-          <t>Tribol CH 1330, 208L E4</t>
+          <t>Tribol CH 1330, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1304">
       <c r="A1304" s="4" t="inlineStr">
         <is>
-          <t>15BA36</t>
+          <t>15E1B3</t>
         </is>
       </c>
       <c r="B1304" s="5" t="inlineStr">
         <is>
-          <t>Tribol CH 1330, 20L E4</t>
+          <t>Tribol CH 1430 spray, 12X.4L LL</t>
         </is>
       </c>
     </row>
     <row r="1305">
       <c r="A1305" s="4" t="inlineStr">
         <is>
-          <t>15E1B3</t>
+          <t>156D6A</t>
         </is>
       </c>
       <c r="B1305" s="5" t="inlineStr">
         <is>
-          <t>Tribol CH 1430 spray, 12X.4L LL</t>
+          <t>Tribol CH 1430, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1306">
       <c r="A1306" s="4" t="inlineStr">
         <is>
-          <t>156D6A</t>
+          <t>156D5C</t>
         </is>
       </c>
       <c r="B1306" s="5" t="inlineStr">
         <is>
-          <t>Tribol CH 1430, 208L AA</t>
+          <t>Tribol CH 1430, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1307">
       <c r="A1307" s="4" t="inlineStr">
         <is>
-          <t>156D5C</t>
+          <t>15B5DF</t>
         </is>
       </c>
       <c r="B1307" s="5" t="inlineStr">
         <is>
-          <t>Tribol CH 1430, 20L AA</t>
+          <t>Tribol CH 1730/100 Spray, 12X.4L HG</t>
         </is>
       </c>
     </row>
     <row r="1308">
       <c r="A1308" s="4" t="inlineStr">
         <is>
-          <t>15B5DF</t>
+          <t>156DDA</t>
         </is>
       </c>
       <c r="B1308" s="5" t="inlineStr">
         <is>
-          <t>Tribol CH 1730/100 Spray, 12X.4L HG</t>
+          <t>Tribol CH 1730/100, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1309">
       <c r="A1309" s="4" t="inlineStr">
         <is>
-          <t>156DDA</t>
+          <t>15B49B</t>
         </is>
       </c>
       <c r="B1309" s="5" t="inlineStr">
         <is>
-          <t>Tribol CH 1730/100, 20L E4</t>
+          <t>Tribol CH 290/150, 18.1K HN</t>
         </is>
       </c>
     </row>
     <row r="1310">
       <c r="A1310" s="4" t="inlineStr">
         <is>
-          <t>15B49B</t>
+          <t>15A7E6</t>
         </is>
       </c>
       <c r="B1310" s="5" t="inlineStr">
         <is>
-          <t>Tribol CH 290/150, 18.1K HN</t>
+          <t>Tribol CH 290/150, 204K AA</t>
         </is>
       </c>
     </row>
     <row r="1311">
       <c r="A1311" s="4" t="inlineStr">
         <is>
-          <t>15A7E6</t>
+          <t>15C8C2</t>
         </is>
       </c>
       <c r="B1311" s="5" t="inlineStr">
         <is>
-          <t>Tribol CH 290/150, 204K AA</t>
+          <t>Tribol CS 1555/46, 60L E4</t>
         </is>
       </c>
     </row>
     <row r="1312">
       <c r="A1312" s="4" t="inlineStr">
         <is>
-          <t>15C8C2</t>
+          <t>15E577</t>
         </is>
       </c>
       <c r="B1312" s="5" t="inlineStr">
         <is>
-          <t>Tribol CS 1555/46, 60L E4</t>
+          <t>Tribol CS 1555/68, 200L EA</t>
         </is>
       </c>
     </row>
     <row r="1313">
       <c r="A1313" s="4" t="inlineStr">
         <is>
-          <t>15E577</t>
+          <t>15CE27</t>
         </is>
       </c>
       <c r="B1313" s="5" t="inlineStr">
         <is>
-          <t>Tribol CS 1555/68, 200L EA</t>
+          <t>Tribol CS 890/100, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1314">
       <c r="A1314" s="4" t="inlineStr">
         <is>
-          <t>15CE27</t>
+          <t>15C83E</t>
         </is>
       </c>
       <c r="B1314" s="5" t="inlineStr">
         <is>
-          <t>Tribol CS 890/100, 20L E4</t>
+          <t>Tribol GR 100-0 PD, 180K AA</t>
         </is>
       </c>
     </row>
     <row r="1315">
       <c r="A1315" s="4" t="inlineStr">
         <is>
-          <t>15C83E</t>
+          <t>15C83D</t>
         </is>
       </c>
       <c r="B1315" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 100-0 PD, 180K AA</t>
+          <t>Tribol GR 100-0 PD, 18K AA</t>
         </is>
       </c>
     </row>
     <row r="1316">
       <c r="A1316" s="4" t="inlineStr">
         <is>
-          <t>15C83D</t>
+          <t>15C840</t>
         </is>
       </c>
       <c r="B1316" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 100-0 PD, 18K AA</t>
+          <t>Tribol GR 100-0 PD, 50K AA</t>
         </is>
       </c>
     </row>
     <row r="1317">
       <c r="A1317" s="4" t="inlineStr">
         <is>
-          <t>15C840</t>
+          <t>15C844</t>
         </is>
       </c>
       <c r="B1317" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 100-0 PD, 50K AA</t>
+          <t>Tribol GR 100-0 PD, 5K IH</t>
         </is>
       </c>
     </row>
     <row r="1318">
       <c r="A1318" s="4" t="inlineStr">
         <is>
-          <t>15C844</t>
+          <t>15C8B6</t>
         </is>
       </c>
       <c r="B1318" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 100-0 PD, 5K IH</t>
+          <t>Tribol GR 100-00 PD, 180K AA</t>
         </is>
       </c>
     </row>
     <row r="1319">
       <c r="A1319" s="4" t="inlineStr">
         <is>
-          <t>15C8B6</t>
+          <t>15C8B4</t>
         </is>
       </c>
       <c r="B1319" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 100-00 PD, 180K AA</t>
+          <t>Tribol GR 100-00 PD, 18K AA</t>
         </is>
       </c>
     </row>
     <row r="1320">
       <c r="A1320" s="4" t="inlineStr">
         <is>
-          <t>15C8B4</t>
+          <t>15C8BA</t>
         </is>
       </c>
       <c r="B1320" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 100-00 PD, 18K AA</t>
+          <t>Tribol GR 100-00 PD, 50K AA</t>
         </is>
       </c>
     </row>
     <row r="1321">
       <c r="A1321" s="4" t="inlineStr">
         <is>
-          <t>15C8BA</t>
+          <t>15C8B8</t>
         </is>
       </c>
       <c r="B1321" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 100-00 PD, 50K AA</t>
+          <t>Tribol GR 100-00 PD, 5K IH</t>
         </is>
       </c>
     </row>
     <row r="1322">
       <c r="A1322" s="4" t="inlineStr">
         <is>
-          <t>15C8B8</t>
+          <t>15C8FD</t>
         </is>
       </c>
       <c r="B1322" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 100-00 PD, 5K IH</t>
+          <t>Tribol GR 100-1 PD, 180K AA</t>
         </is>
       </c>
     </row>
     <row r="1323">
       <c r="A1323" s="4" t="inlineStr">
         <is>
-          <t>15C8FD</t>
+          <t>15C8FB</t>
         </is>
       </c>
       <c r="B1323" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 100-1 PD, 180K AA</t>
+          <t>Tribol GR 100-1 PD, 18K AA</t>
         </is>
       </c>
     </row>
     <row r="1324">
       <c r="A1324" s="4" t="inlineStr">
         <is>
-          <t>15C8FB</t>
+          <t>15C902</t>
         </is>
       </c>
       <c r="B1324" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 100-1 PD, 18K AA</t>
+          <t>Tribol GR 100-1 PD, 20X.4K IH</t>
         </is>
       </c>
     </row>
     <row r="1325">
       <c r="A1325" s="4" t="inlineStr">
         <is>
-          <t>15C902</t>
+          <t>15C8FF</t>
         </is>
       </c>
       <c r="B1325" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 100-1 PD, 20X.4K IH</t>
+          <t>Tribol GR 100-1 PD, 50K AA</t>
         </is>
       </c>
     </row>
     <row r="1326">
       <c r="A1326" s="4" t="inlineStr">
         <is>
-          <t>15C8FF</t>
+          <t>15C855</t>
         </is>
       </c>
       <c r="B1326" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 100-1 PD, 50K AA</t>
+          <t>Tribol GR 100-2 PD, 180K AA</t>
         </is>
       </c>
     </row>
     <row r="1327">
       <c r="A1327" s="4" t="inlineStr">
         <is>
-          <t>15C855</t>
+          <t>15C854</t>
         </is>
       </c>
       <c r="B1327" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 100-2 PD, 180K AA</t>
+          <t>Tribol GR 100-2 PD, 18K AA</t>
         </is>
       </c>
     </row>
     <row r="1328">
       <c r="A1328" s="4" t="inlineStr">
         <is>
-          <t>15C854</t>
+          <t>15C852</t>
         </is>
       </c>
       <c r="B1328" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 100-2 PD, 18K AA</t>
+          <t>Tribol GR 100-2 PD, 20X.4K IH</t>
         </is>
       </c>
     </row>
     <row r="1329">
       <c r="A1329" s="4" t="inlineStr">
         <is>
-          <t>15C852</t>
+          <t>15C857</t>
         </is>
       </c>
       <c r="B1329" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 100-2 PD, 20X.4K IH</t>
+          <t>Tribol GR 100-2 PD, 50K AA</t>
         </is>
       </c>
     </row>
     <row r="1330">
       <c r="A1330" s="4" t="inlineStr">
         <is>
-          <t>15C857</t>
+          <t>15C856</t>
         </is>
       </c>
       <c r="B1330" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 100-2 PD, 50K AA</t>
+          <t>Tribol GR 100-2 PD, 5K IQ</t>
         </is>
       </c>
     </row>
     <row r="1331">
       <c r="A1331" s="4" t="inlineStr">
         <is>
-          <t>15C856</t>
+          <t>15C8D0</t>
         </is>
       </c>
       <c r="B1331" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 100-2 PD, 5K IQ</t>
+          <t>Tribol GR 1350-2.5 PD, 180K AA</t>
         </is>
       </c>
     </row>
     <row r="1332">
       <c r="A1332" s="4" t="inlineStr">
         <is>
-          <t>15C8D0</t>
+          <t>15C8CD</t>
         </is>
       </c>
       <c r="B1332" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 1350-2.5 PD, 180K AA</t>
+          <t>Tribol GR 1350-2.5 PD, 18K AA</t>
         </is>
       </c>
     </row>
     <row r="1333">
       <c r="A1333" s="4" t="inlineStr">
         <is>
-          <t>15C8CD</t>
+          <t>15C8D4</t>
         </is>
       </c>
       <c r="B1333" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 1350-2.5 PD, 18K AA</t>
+          <t>Tribol GR 1350-2.5 PD, 20X.4K IQ</t>
         </is>
       </c>
     </row>
     <row r="1334">
       <c r="A1334" s="4" t="inlineStr">
         <is>
-          <t>15C8D4</t>
+          <t>15C8D3</t>
         </is>
       </c>
       <c r="B1334" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 1350-2.5 PD, 20X.4K IQ</t>
+          <t>Tribol GR 1350-2.5 PD, 50K AA</t>
         </is>
       </c>
     </row>
     <row r="1335">
       <c r="A1335" s="4" t="inlineStr">
         <is>
-          <t>15C8D3</t>
+          <t>158CA2</t>
         </is>
       </c>
       <c r="B1335" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 1350-2.5 PD, 50K AA</t>
+          <t>Tribol GR 2 EP, 180K E4</t>
         </is>
       </c>
     </row>
     <row r="1336">
       <c r="A1336" s="4" t="inlineStr">
         <is>
-          <t>158CA2</t>
+          <t>158CA1</t>
         </is>
       </c>
       <c r="B1336" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 2 EP, 180K E4</t>
+          <t>Tribol GR 2 EP, 18K E4</t>
         </is>
       </c>
     </row>
     <row r="1337">
       <c r="A1337" s="4" t="inlineStr">
         <is>
-          <t>158CA1</t>
+          <t>15ACF5</t>
         </is>
       </c>
       <c r="B1337" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 2 EP, 18K E4</t>
+          <t>Tribol GR 2 EP, 5K E4</t>
         </is>
       </c>
     </row>
     <row r="1338">
       <c r="A1338" s="4" t="inlineStr">
         <is>
-          <t>15ACF5</t>
+          <t>15770B</t>
         </is>
       </c>
       <c r="B1338" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 2 EP, 5K E4</t>
+          <t>Tribol GR 3020/1000-00 PD, 18K E4</t>
         </is>
       </c>
     </row>
     <row r="1339">
       <c r="A1339" s="4" t="inlineStr">
         <is>
-          <t>15770B</t>
+          <t>15770E</t>
         </is>
       </c>
       <c r="B1339" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 3020/1000-00 PD, 18K E4</t>
+          <t>Tribol GR 3020/1000-00 PD, 52K E4</t>
         </is>
       </c>
     </row>
     <row r="1340">
       <c r="A1340" s="4" t="inlineStr">
         <is>
-          <t>15770E</t>
+          <t>1571F0</t>
         </is>
       </c>
       <c r="B1340" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 3020/1000-00 PD, 52K E4</t>
+          <t>Tribol GR 3020/1000-000 PD, 18K E4</t>
         </is>
       </c>
     </row>
     <row r="1341">
       <c r="A1341" s="4" t="inlineStr">
         <is>
-          <t>1571F0</t>
+          <t>15E5E4</t>
         </is>
       </c>
       <c r="B1341" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 3020/1000-000 PD, 18K E4</t>
+          <t>Tribol GR 3020/1000-1 PD, 18K 1E</t>
         </is>
       </c>
     </row>
     <row r="1342">
       <c r="A1342" s="4" t="inlineStr">
         <is>
-          <t>15E5E4</t>
+          <t>15888A</t>
         </is>
       </c>
       <c r="B1342" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 3020/1000-1 PD, 18K 1E</t>
+          <t>Tribol GR 3020/1000-1 PD, 18K E4</t>
         </is>
       </c>
     </row>
     <row r="1343">
       <c r="A1343" s="4" t="inlineStr">
         <is>
-          <t>15888A</t>
+          <t>15B188</t>
         </is>
       </c>
       <c r="B1343" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 3020/1000-1 PD, 18K E4</t>
+          <t>Tribol GR 3020/1000-2 PD, 50X.4K E4</t>
         </is>
       </c>
     </row>
     <row r="1344">
       <c r="A1344" s="4" t="inlineStr">
         <is>
-          <t>15B188</t>
+          <t>156F58</t>
         </is>
       </c>
       <c r="B1344" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 3020/1000-2 PD, 50X.4K E4</t>
+          <t>Tribol GR 3020/1000-2 PD, 52K E4</t>
         </is>
       </c>
     </row>
     <row r="1345">
       <c r="A1345" s="4" t="inlineStr">
         <is>
-          <t>156F58</t>
+          <t>15E5E3</t>
         </is>
       </c>
       <c r="B1345" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 3020/1000-2 PD, 52K E4</t>
+          <t>Tribol GR 400-2 PD, 18K 1E</t>
         </is>
       </c>
     </row>
     <row r="1346">
       <c r="A1346" s="4" t="inlineStr">
         <is>
-          <t>15E5E3</t>
+          <t>15CC35</t>
         </is>
       </c>
       <c r="B1346" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 400-2 PD, 18K 1E</t>
+          <t>Tribol GR 400-2 PD, 18K E4</t>
         </is>
       </c>
     </row>
     <row r="1347">
       <c r="A1347" s="4" t="inlineStr">
         <is>
-          <t>15CC35</t>
+          <t>15CC39</t>
         </is>
       </c>
       <c r="B1347" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 400-2 PD, 18K E4</t>
+          <t>Tribol GR 400-2 PD, 20X.4K E4</t>
         </is>
       </c>
     </row>
     <row r="1348">
       <c r="A1348" s="4" t="inlineStr">
         <is>
-          <t>15CC39</t>
+          <t>15CC38</t>
         </is>
       </c>
       <c r="B1348" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 400-2 PD, 20X.4K E4</t>
+          <t>Tribol GR 400-2 PD, 50K E4</t>
         </is>
       </c>
     </row>
     <row r="1349">
       <c r="A1349" s="4" t="inlineStr">
         <is>
-          <t>15CC38</t>
+          <t>158BBE</t>
         </is>
       </c>
       <c r="B1349" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 400-2 PD, 50K E4</t>
+          <t>Tribol GR 400-3 PD, 18K E4</t>
         </is>
       </c>
     </row>
     <row r="1350">
       <c r="A1350" s="4" t="inlineStr">
         <is>
-          <t>158BBE</t>
+          <t>15942F</t>
         </is>
       </c>
       <c r="B1350" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 400-3 PD, 18K E4</t>
+          <t>Tribol GR 4020/220-1 PD, 18K E4</t>
         </is>
       </c>
     </row>
     <row r="1351">
       <c r="A1351" s="4" t="inlineStr">
         <is>
-          <t>15942F</t>
+          <t>15942D</t>
         </is>
       </c>
       <c r="B1351" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 4020/220-1 PD, 18K E4</t>
+          <t>Tribol GR 4020/220-1 PD, 190K E4</t>
         </is>
       </c>
     </row>
     <row r="1352">
       <c r="A1352" s="4" t="inlineStr">
         <is>
-          <t>15942D</t>
+          <t>15942E</t>
         </is>
       </c>
       <c r="B1352" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 4020/220-1 PD, 190K E4</t>
+          <t>Tribol GR 4020/220-1 PD, 52K E4</t>
         </is>
       </c>
     </row>
     <row r="1353">
       <c r="A1353" s="4" t="inlineStr">
         <is>
-          <t>15942E</t>
+          <t>1582EB</t>
         </is>
       </c>
       <c r="B1353" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 4020/220-1 PD, 52K E4</t>
+          <t>Tribol GR 4020/220-2 PD, 18K E4</t>
         </is>
       </c>
     </row>
     <row r="1354">
       <c r="A1354" s="4" t="inlineStr">
         <is>
-          <t>1582EB</t>
+          <t>1582DF</t>
         </is>
       </c>
       <c r="B1354" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 4020/220-2 PD, 18K E4</t>
+          <t>Tribol GR 4020/220-2 PD, 190K E4</t>
         </is>
       </c>
     </row>
     <row r="1355">
       <c r="A1355" s="4" t="inlineStr">
         <is>
-          <t>1582DF</t>
+          <t>15B02C</t>
         </is>
       </c>
       <c r="B1355" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 4020/220-2 PD, 190K E4</t>
+          <t>Tribol GR 4020/220-2 PD, 50X.4K E4</t>
         </is>
       </c>
     </row>
     <row r="1356">
       <c r="A1356" s="4" t="inlineStr">
         <is>
-          <t>15B02C</t>
+          <t>1582EE</t>
         </is>
       </c>
       <c r="B1356" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 4020/220-2 PD, 50X.4K E4</t>
+          <t>Tribol GR 4020/220-2 PD, 52K E4</t>
         </is>
       </c>
     </row>
     <row r="1357">
       <c r="A1357" s="4" t="inlineStr">
         <is>
-          <t>1582EE</t>
+          <t>1578A9</t>
         </is>
       </c>
       <c r="B1357" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 4020/220-2 PD, 52K E4</t>
+          <t>Tribol GR 4020/460-2 PD, 18K E4</t>
         </is>
       </c>
     </row>
     <row r="1358">
       <c r="A1358" s="4" t="inlineStr">
         <is>
-          <t>1578A9</t>
+          <t>1578A8</t>
         </is>
       </c>
       <c r="B1358" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 4020/460-2 PD, 18K E4</t>
+          <t>Tribol GR 4020/460-2 PD, 190K E4</t>
         </is>
       </c>
     </row>
     <row r="1359">
       <c r="A1359" s="4" t="inlineStr">
         <is>
-          <t>1578A8</t>
+          <t>157C4C</t>
         </is>
       </c>
       <c r="B1359" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 4020/460-2 PD, 190K E4</t>
+          <t>Tribol GR 4747/220-2 HT, 185K E4</t>
         </is>
       </c>
     </row>
     <row r="1360">
       <c r="A1360" s="4" t="inlineStr">
         <is>
-          <t>157C4C</t>
+          <t>157C4B</t>
         </is>
       </c>
       <c r="B1360" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 4747/220-2 HT, 185K E4</t>
+          <t>Tribol GR 4747/220-2 HT, 18K E4</t>
         </is>
       </c>
     </row>
     <row r="1361">
       <c r="A1361" s="4" t="inlineStr">
         <is>
-          <t>157C4B</t>
+          <t>157C4A</t>
         </is>
       </c>
       <c r="B1361" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 4747/220-2 HT, 18K E4</t>
+          <t>Tribol GR 4747/220-2 HT, 52K E4</t>
         </is>
       </c>
     </row>
     <row r="1362">
       <c r="A1362" s="4" t="inlineStr">
         <is>
-          <t>157C4A</t>
+          <t>15DEC5</t>
         </is>
       </c>
       <c r="B1362" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR 4747/220-2 HT, 52K E4</t>
+          <t>Tribol GR ALR 100-00 PD, 18K LD</t>
         </is>
       </c>
     </row>
     <row r="1363">
       <c r="A1363" s="4" t="inlineStr">
         <is>
-          <t>15DEC5</t>
+          <t>158DA3</t>
         </is>
       </c>
       <c r="B1363" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR ALR 100-00 PD, 18K LD</t>
+          <t>Tribol GR CLS 000, 18K E4</t>
         </is>
       </c>
     </row>
     <row r="1364">
       <c r="A1364" s="4" t="inlineStr">
         <is>
-          <t>158DA3</t>
+          <t>15773E</t>
         </is>
       </c>
       <c r="B1364" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR CLS 000, 18K E4</t>
+          <t>Tribol GR CLS 2, 18K AA</t>
         </is>
       </c>
     </row>
     <row r="1365">
       <c r="A1365" s="4" t="inlineStr">
         <is>
-          <t>15773E</t>
+          <t>15B17E</t>
         </is>
       </c>
       <c r="B1365" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR CLS 2, 18K AA</t>
+          <t>Tribol GR CLS 2, 20X.4K IQ</t>
         </is>
       </c>
     </row>
     <row r="1366">
       <c r="A1366" s="4" t="inlineStr">
         <is>
-          <t>15B17E</t>
+          <t>157CD9</t>
         </is>
       </c>
       <c r="B1366" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR CLS 2, 20X.4K IQ</t>
+          <t>Tribol GR ES 2, 18K E4</t>
         </is>
       </c>
     </row>
     <row r="1367">
       <c r="A1367" s="4" t="inlineStr">
         <is>
-          <t>157CD9</t>
+          <t>157CDA</t>
         </is>
       </c>
       <c r="B1367" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR ES 2, 18K E4</t>
+          <t>Tribol GR ES 2, 4X.36K AA</t>
         </is>
       </c>
     </row>
     <row r="1368">
       <c r="A1368" s="4" t="inlineStr">
         <is>
-          <t>157CDA</t>
+          <t>15A220</t>
         </is>
       </c>
       <c r="B1368" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR ES 2, 4X.36K AA</t>
+          <t>Tribol GR HS 1.5, 4X.375K E4</t>
         </is>
       </c>
     </row>
     <row r="1369">
       <c r="A1369" s="4" t="inlineStr">
         <is>
-          <t>15A220</t>
+          <t>15829A</t>
         </is>
       </c>
       <c r="B1369" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR HS 1.5, 4X.375K E4</t>
+          <t>Tribol GR HS 1.5, 5X1K AD</t>
         </is>
       </c>
     </row>
     <row r="1370">
       <c r="A1370" s="4" t="inlineStr">
         <is>
-          <t>15829A</t>
+          <t>15C87C</t>
         </is>
       </c>
       <c r="B1370" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR HS 1.5, 5X1K AD</t>
+          <t>Tribol GR HT 2, 18K AA</t>
         </is>
       </c>
     </row>
     <row r="1371">
       <c r="A1371" s="4" t="inlineStr">
         <is>
-          <t>15C87C</t>
+          <t>15C881</t>
         </is>
       </c>
       <c r="B1371" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR HT 2, 18K AA</t>
+          <t>Tribol GR HT 2, 20X.4K AA</t>
         </is>
       </c>
     </row>
     <row r="1372">
       <c r="A1372" s="4" t="inlineStr">
         <is>
-          <t>15C881</t>
+          <t>15C880</t>
         </is>
       </c>
       <c r="B1372" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR HT 2, 20X.4K AA</t>
+          <t>Tribol GR HT 2, 50K AA</t>
         </is>
       </c>
     </row>
     <row r="1373">
       <c r="A1373" s="4" t="inlineStr">
         <is>
-          <t>15C880</t>
+          <t>15C87F</t>
         </is>
       </c>
       <c r="B1373" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR HT 2, 50K AA</t>
+          <t>Tribol GR HT 2, 5K AA</t>
         </is>
       </c>
     </row>
     <row r="1374">
       <c r="A1374" s="4" t="inlineStr">
         <is>
-          <t>15C87F</t>
+          <t>156C0D</t>
         </is>
       </c>
       <c r="B1374" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR HT 2, 5K AA</t>
+          <t>Tribol GR PS 1 HT, 180K E4</t>
         </is>
       </c>
     </row>
     <row r="1375">
       <c r="A1375" s="4" t="inlineStr">
         <is>
-          <t>156C0D</t>
+          <t>156C0A</t>
         </is>
       </c>
       <c r="B1375" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR PS 1 HT, 180K E4</t>
+          <t>Tribol GR PS 1 HT, 18K E4</t>
         </is>
       </c>
     </row>
     <row r="1376">
       <c r="A1376" s="4" t="inlineStr">
         <is>
-          <t>156C0A</t>
+          <t>156C0F</t>
         </is>
       </c>
       <c r="B1376" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR PS 1 HT, 18K E4</t>
+          <t>Tribol GR PS 2 HT, 18K E4</t>
         </is>
       </c>
     </row>
     <row r="1377">
       <c r="A1377" s="4" t="inlineStr">
         <is>
-          <t>156C0F</t>
+          <t>15CD74</t>
         </is>
       </c>
       <c r="B1377" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR PS 2 HT, 18K E4</t>
+          <t>Tribol GR SW 460-1, 180K AA</t>
         </is>
       </c>
     </row>
     <row r="1378">
       <c r="A1378" s="4" t="inlineStr">
         <is>
-          <t>15CD74</t>
+          <t>15CD73</t>
         </is>
       </c>
       <c r="B1378" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR SW 460-1, 180K AA</t>
+          <t>Tribol GR SW 460-1, 18K AA</t>
         </is>
       </c>
     </row>
     <row r="1379">
       <c r="A1379" s="4" t="inlineStr">
         <is>
-          <t>15CD73</t>
+          <t>15CD75</t>
         </is>
       </c>
       <c r="B1379" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR SW 460-1, 18K AA</t>
+          <t>Tribol GR SW 460-1, 20X.4K H8</t>
         </is>
       </c>
     </row>
     <row r="1380">
       <c r="A1380" s="4" t="inlineStr">
         <is>
-          <t>15CD75</t>
+          <t>15C862</t>
         </is>
       </c>
       <c r="B1380" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR SW 460-1, 20X.4K H8</t>
+          <t>Tribol GR TT 1 PD, 50K E4</t>
         </is>
       </c>
     </row>
     <row r="1381">
       <c r="A1381" s="4" t="inlineStr">
         <is>
-          <t>15C862</t>
+          <t>15C861</t>
         </is>
       </c>
       <c r="B1381" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR TT 1 PD, 50K E4</t>
+          <t>Tribol GR TT 1 PD, 5K E4</t>
         </is>
       </c>
     </row>
     <row r="1382">
       <c r="A1382" s="4" t="inlineStr">
         <is>
-          <t>15C861</t>
+          <t>15866C</t>
         </is>
       </c>
       <c r="B1382" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR TT 1 PD, 5K E4</t>
+          <t>Tribol GR TT1 EP, 50K E4</t>
         </is>
       </c>
     </row>
     <row r="1383">
       <c r="A1383" s="4" t="inlineStr">
         <is>
-          <t>15866C</t>
+          <t>157F0A</t>
         </is>
       </c>
       <c r="B1383" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR TT1 EP, 50K E4</t>
+          <t>Tribol GR XT 2 HT, 180K E4</t>
         </is>
       </c>
     </row>
     <row r="1384">
       <c r="A1384" s="4" t="inlineStr">
         <is>
-          <t>157F0A</t>
+          <t>157F06</t>
         </is>
       </c>
       <c r="B1384" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR XT 2 HT, 180K E4</t>
+          <t>Tribol GR XT 2 HT, 18K E4</t>
         </is>
       </c>
     </row>
     <row r="1385">
       <c r="A1385" s="4" t="inlineStr">
         <is>
-          <t>157F06</t>
+          <t>15B2AA</t>
         </is>
       </c>
       <c r="B1385" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR XT 2 HT, 18K E4</t>
+          <t>Tribol GR XT 2 HT, 4X.4K E4</t>
         </is>
       </c>
     </row>
     <row r="1386">
       <c r="A1386" s="4" t="inlineStr">
         <is>
-          <t>15B2AA</t>
+          <t>15AE2D</t>
         </is>
       </c>
       <c r="B1386" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR XT 2 HT, 4X.4K E4</t>
+          <t>Tribol GR XT 2 HT, 5K E4</t>
         </is>
       </c>
     </row>
     <row r="1387">
       <c r="A1387" s="4" t="inlineStr">
         <is>
-          <t>15AE2D</t>
+          <t>15725C</t>
         </is>
       </c>
       <c r="B1387" s="5" t="inlineStr">
         <is>
-          <t>Tribol GR XT 2 HT, 5K E4</t>
+          <t>Tribol HM 943/32, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1388">
       <c r="A1388" s="4" t="inlineStr">
         <is>
-          <t>15725C</t>
+          <t>15703B</t>
         </is>
       </c>
       <c r="B1388" s="5" t="inlineStr">
         <is>
-          <t>Tribol HM 943/32, 208L E4</t>
+          <t>Tribol HM 943/46, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1389">
       <c r="A1389" s="4" t="inlineStr">
         <is>
-          <t>15703B</t>
+          <t>159FBA</t>
         </is>
       </c>
       <c r="B1389" s="5" t="inlineStr">
         <is>
-          <t>Tribol HM 943/46, 208L E4</t>
+          <t>Tribol MO 14, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1390">
       <c r="A1390" s="4" t="inlineStr">
         <is>
-          <t>159FBA</t>
+          <t>156ACC</t>
         </is>
       </c>
       <c r="B1390" s="5" t="inlineStr">
         <is>
-          <t>Tribol MO 14, 20L E4</t>
+          <t>Tribol OG 500-0, 18K AA</t>
         </is>
       </c>
     </row>
     <row r="1391">
       <c r="A1391" s="4" t="inlineStr">
         <is>
-          <t>156ACC</t>
+          <t>15788D</t>
         </is>
       </c>
       <c r="B1391" s="5" t="inlineStr">
         <is>
-          <t>Tribol OG 500-0, 18K AA</t>
+          <t>Tribol PM 320 S, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1392">
       <c r="A1392" s="4" t="inlineStr">
         <is>
-          <t>15788D</t>
+          <t>15788C</t>
         </is>
       </c>
       <c r="B1392" s="5" t="inlineStr">
         <is>
-          <t>Tribol PM 320 S, 208L E4</t>
+          <t>Tribol PM 320 S, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1393">
       <c r="A1393" s="4" t="inlineStr">
         <is>
-          <t>15788C</t>
+          <t>15D511</t>
         </is>
       </c>
       <c r="B1393" s="5" t="inlineStr">
         <is>
-          <t>Tribol PM 320 S, 20L E4</t>
+          <t>Variocut B 27, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1394">
       <c r="A1394" s="4" t="inlineStr">
         <is>
-          <t>15D511</t>
+          <t>1558C2</t>
         </is>
       </c>
       <c r="B1394" s="5" t="inlineStr">
         <is>
-          <t>Variocut B 27, 208L AA</t>
+          <t>Variocut B 30 SP, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1395">
       <c r="A1395" s="4" t="inlineStr">
         <is>
-          <t>1558C2</t>
+          <t>15094D</t>
         </is>
       </c>
       <c r="B1395" s="5" t="inlineStr">
         <is>
-          <t>Variocut B 30 SP, 208L E4</t>
+          <t>Variocut B 30, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1396">
       <c r="A1396" s="4" t="inlineStr">
         <is>
-          <t>15094D</t>
+          <t>151ACF</t>
         </is>
       </c>
       <c r="B1396" s="5" t="inlineStr">
         <is>
-          <t>Variocut B 30, 208L E4</t>
+          <t>Variocut B 30, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1397">
       <c r="A1397" s="4" t="inlineStr">
         <is>
-          <t>151ACF</t>
+          <t>15AC48</t>
         </is>
       </c>
       <c r="B1397" s="5" t="inlineStr">
         <is>
-          <t>Variocut B 30, 20L E4</t>
+          <t>Variocut B 46 TC, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1398">
       <c r="A1398" s="4" t="inlineStr">
         <is>
-          <t>15AC48</t>
+          <t>15AC47</t>
         </is>
       </c>
       <c r="B1398" s="5" t="inlineStr">
         <is>
-          <t>Variocut B 46 TC, 208L AA</t>
+          <t>Variocut B 46 TC, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1399">
       <c r="A1399" s="4" t="inlineStr">
         <is>
-          <t>15AC47</t>
+          <t>1571F6</t>
         </is>
       </c>
       <c r="B1399" s="5" t="inlineStr">
         <is>
-          <t>Variocut B 46 TC, 20L AA</t>
+          <t>Variocut B 9, 208L HB</t>
         </is>
       </c>
     </row>
     <row r="1400">
       <c r="A1400" s="4" t="inlineStr">
         <is>
-          <t>1571F6</t>
+          <t>154F7E</t>
         </is>
       </c>
       <c r="B1400" s="5" t="inlineStr">
         <is>
-          <t>Variocut B 9, 208L HB</t>
+          <t>Variocut C 334, 1000L AA</t>
         </is>
       </c>
     </row>
     <row r="1401">
       <c r="A1401" s="4" t="inlineStr">
         <is>
-          <t>154F7E</t>
+          <t>154F80</t>
         </is>
       </c>
       <c r="B1401" s="5" t="inlineStr">
         <is>
-          <t>Variocut C 334, 1000L AA</t>
+          <t>Variocut C 334, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1402">
       <c r="A1402" s="4" t="inlineStr">
         <is>
-          <t>154F80</t>
+          <t>1553F0</t>
         </is>
       </c>
       <c r="B1402" s="5" t="inlineStr">
         <is>
-          <t>Variocut C 334, 208L AA</t>
+          <t>Variocut C 462, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1403">
       <c r="A1403" s="4" t="inlineStr">
         <is>
-          <t>1553F0</t>
+          <t>1553EF</t>
         </is>
       </c>
       <c r="B1403" s="5" t="inlineStr">
         <is>
-          <t>Variocut C 462, 208L E4</t>
+          <t>Variocut C 462, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1404">
       <c r="A1404" s="4" t="inlineStr">
         <is>
-          <t>1553EF</t>
+          <t>15E8C2</t>
         </is>
       </c>
       <c r="B1404" s="5" t="inlineStr">
         <is>
-          <t>Variocut C 462, 20L E4</t>
+          <t>Variocut C 814 HC, 1000L AA</t>
         </is>
       </c>
     </row>
     <row r="1405">
       <c r="A1405" s="4" t="inlineStr">
         <is>
-          <t>15E8C2</t>
+          <t>15E8C1</t>
         </is>
       </c>
       <c r="B1405" s="5" t="inlineStr">
         <is>
-          <t>Variocut C 814 HC, 1000L AA</t>
+          <t>Variocut C 814 HC, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1406">
       <c r="A1406" s="4" t="inlineStr">
         <is>
-          <t>15E8C1</t>
+          <t>15B90C</t>
         </is>
       </c>
       <c r="B1406" s="5" t="inlineStr">
         <is>
-          <t>Variocut C 814 HC, 208L AA</t>
+          <t>Variocut D 270, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1407">
       <c r="A1407" s="4" t="inlineStr">
         <is>
-          <t>15B90C</t>
+          <t>1557DC</t>
         </is>
       </c>
       <c r="B1407" s="5" t="inlineStr">
         <is>
-          <t>Variocut D 270, 208L AA</t>
+          <t>Variocut D 730, 208L KF</t>
         </is>
       </c>
     </row>
     <row r="1408">
       <c r="A1408" s="4" t="inlineStr">
         <is>
-          <t>1557DC</t>
+          <t>1557EC</t>
         </is>
       </c>
       <c r="B1408" s="5" t="inlineStr">
         <is>
-          <t>Variocut D 730, 208L KF</t>
+          <t>Variocut D 734, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1409">
       <c r="A1409" s="4" t="inlineStr">
         <is>
-          <t>1557EC</t>
+          <t>15A1A1</t>
         </is>
       </c>
       <c r="B1409" s="5" t="inlineStr">
         <is>
-          <t>Variocut D 734, 208L AA</t>
+          <t>Variocut G 260, 1000L HA</t>
         </is>
       </c>
     </row>
     <row r="1410">
       <c r="A1410" s="4" t="inlineStr">
         <is>
-          <t>15A1A1</t>
+          <t>1588DD</t>
         </is>
       </c>
       <c r="B1410" s="5" t="inlineStr">
         <is>
-          <t>Variocut G 260, 1000L HA</t>
+          <t>Variocut G 260, 208L HA</t>
         </is>
       </c>
     </row>
     <row r="1411">
       <c r="A1411" s="4" t="inlineStr">
         <is>
-          <t>1588DD</t>
+          <t>217BC8</t>
         </is>
       </c>
       <c r="B1411" s="5" t="inlineStr">
         <is>
-          <t>Variocut G 260, 208L HA</t>
+          <t>Variocut G 260, Bulk</t>
         </is>
       </c>
     </row>
     <row r="1412">
       <c r="A1412" s="4" t="inlineStr">
         <is>
-          <t>217BC8</t>
+          <t>1558C9</t>
         </is>
       </c>
       <c r="B1412" s="5" t="inlineStr">
         <is>
-          <t>Variocut G 260, Bulk</t>
+          <t>Variocut G 399, 1000L AA</t>
         </is>
       </c>
     </row>
     <row r="1413">
       <c r="A1413" s="4" t="inlineStr">
         <is>
-          <t>1558C9</t>
+          <t>1558C6</t>
         </is>
       </c>
       <c r="B1413" s="5" t="inlineStr">
         <is>
-          <t>Variocut G 399, 1000L AA</t>
+          <t>Variocut G 399, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1414">
       <c r="A1414" s="4" t="inlineStr">
         <is>
-          <t>1558C6</t>
+          <t>155C54</t>
         </is>
       </c>
       <c r="B1414" s="5" t="inlineStr">
         <is>
-          <t>Variocut G 399, 208L AA</t>
+          <t>Variocut G 408 HC, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1415">
       <c r="A1415" s="4" t="inlineStr">
         <is>
-          <t>155C54</t>
+          <t>464102</t>
         </is>
       </c>
       <c r="B1415" s="5" t="inlineStr">
         <is>
-          <t>Variocut G 408 HC, 208L AA</t>
+          <t>Variocut G 600 HC, Bulk</t>
         </is>
       </c>
     </row>
     <row r="1416">
       <c r="A1416" s="4" t="inlineStr">
         <is>
-          <t>464102</t>
+          <t>155B6C</t>
         </is>
       </c>
       <c r="B1416" s="5" t="inlineStr">
         <is>
-          <t>Variocut G 600 HC, Bulk</t>
+          <t>Variocut G 600 HC, 1000L AA</t>
         </is>
       </c>
     </row>
     <row r="1417">
       <c r="A1417" s="4" t="inlineStr">
         <is>
-          <t>155B6C</t>
+          <t>155B68</t>
         </is>
       </c>
       <c r="B1417" s="5" t="inlineStr">
         <is>
-          <t>Variocut G 600 HC, 1000L AA</t>
+          <t>Variocut G 600 HC, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1418">
       <c r="A1418" s="4" t="inlineStr">
         <is>
-          <t>155B68</t>
+          <t>155B70</t>
         </is>
       </c>
       <c r="B1418" s="5" t="inlineStr">
         <is>
-          <t>Variocut G 600 HC, 208L AA</t>
+          <t>Variocut G 600 HC, 20L AA</t>
         </is>
       </c>
     </row>
     <row r="1419">
       <c r="A1419" s="4" t="inlineStr">
         <is>
-          <t>155B70</t>
+          <t>216C12</t>
         </is>
       </c>
       <c r="B1419" s="5" t="inlineStr">
         <is>
-          <t>Variocut G 600 HC, 20L AA</t>
+          <t>Variocut G 600 HC, Bulk</t>
         </is>
       </c>
     </row>
     <row r="1420">
       <c r="A1420" s="4" t="inlineStr">
         <is>
-          <t>216C12</t>
+          <t>15DEDB</t>
         </is>
       </c>
       <c r="B1420" s="5" t="inlineStr">
         <is>
-          <t>Variocut G 600 HC, Bulk</t>
+          <t>Variocut G 611, 1000L KJ</t>
         </is>
       </c>
     </row>
     <row r="1421">
       <c r="A1421" s="4" t="inlineStr">
         <is>
-          <t>15DEDB</t>
+          <t>15DEDC</t>
         </is>
       </c>
       <c r="B1421" s="5" t="inlineStr">
         <is>
-          <t>Variocut G 611, 1000L KJ</t>
+          <t>Variocut G 611, 208L KJ</t>
         </is>
       </c>
     </row>
     <row r="1422">
       <c r="A1422" s="4" t="inlineStr">
         <is>
-          <t>15DEDC</t>
+          <t>155EC4</t>
         </is>
       </c>
       <c r="B1422" s="5" t="inlineStr">
         <is>
-          <t>Variocut G 611, 208L KJ</t>
+          <t>Variocut G 650 HC, 1000L AA</t>
         </is>
       </c>
     </row>
     <row r="1423">
       <c r="A1423" s="4" t="inlineStr">
         <is>
-          <t>155EC4</t>
+          <t>155EC6</t>
         </is>
       </c>
       <c r="B1423" s="5" t="inlineStr">
         <is>
-          <t>Variocut G 650 HC, 1000L AA</t>
+          <t>Variocut G 650 HC, 208L AA</t>
         </is>
       </c>
     </row>
     <row r="1424">
       <c r="A1424" s="4" t="inlineStr">
         <is>
-          <t>155EC6</t>
+          <t>15C347</t>
         </is>
       </c>
       <c r="B1424" s="5" t="inlineStr">
         <is>
-          <t>Variocut G 650 HC, 208L AA</t>
+          <t>Variocut G 950, 1000L AA</t>
         </is>
       </c>
     </row>
     <row r="1425">
       <c r="A1425" s="4" t="inlineStr">
         <is>
-          <t>15C347</t>
+          <t>15AB3F</t>
         </is>
       </c>
       <c r="B1425" s="5" t="inlineStr">
         <is>
-          <t>Variocut G 950, 1000L AA</t>
+          <t>Variocut G 950, 1000L HH</t>
         </is>
       </c>
     </row>
     <row r="1426">
       <c r="A1426" s="4" t="inlineStr">
         <is>
-          <t>15AB3F</t>
+          <t>15E69F</t>
         </is>
       </c>
       <c r="B1426" s="5" t="inlineStr">
         <is>
-          <t>Variocut G 950, 1000L HH</t>
+          <t>Variocut G 950, 1000L HN</t>
         </is>
       </c>
     </row>
     <row r="1427">
       <c r="A1427" s="4" t="inlineStr">
         <is>
-          <t>15E69F</t>
+          <t>15758D</t>
         </is>
       </c>
       <c r="B1427" s="5" t="inlineStr">
         <is>
-          <t>Variocut G 950, 1000L HN</t>
+          <t>Viscogen 3N, 1000L E4</t>
         </is>
       </c>
     </row>
     <row r="1428">
       <c r="A1428" s="4" t="inlineStr">
         <is>
-          <t>15758D</t>
+          <t>15758B</t>
         </is>
       </c>
       <c r="B1428" s="5" t="inlineStr">
         <is>
-          <t>Viscogen 3N, 1000L E4</t>
+          <t>Viscogen 3N, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1429">
       <c r="A1429" s="4" t="inlineStr">
         <is>
-          <t>15758B</t>
+          <t>14BE8A</t>
         </is>
       </c>
       <c r="B1429" s="5" t="inlineStr">
         <is>
-          <t>Viscogen 3N, 208L E4</t>
+          <t>Viscogen KL 15, 20L E7</t>
         </is>
       </c>
     </row>
     <row r="1430">
       <c r="A1430" s="4" t="inlineStr">
         <is>
-          <t>14BE8A</t>
+          <t>15E1B9</t>
         </is>
       </c>
       <c r="B1430" s="5" t="inlineStr">
         <is>
-          <t>Viscogen KL 15, 20L E7</t>
+          <t>Viscogen KL 23 Spray, 12X.4L LL</t>
         </is>
       </c>
     </row>
     <row r="1431">
       <c r="A1431" s="4" t="inlineStr">
         <is>
-          <t>15E1B9</t>
+          <t>14CAE3</t>
         </is>
       </c>
       <c r="B1431" s="5" t="inlineStr">
         <is>
-          <t>Viscogen KL 23 Spray, 12X.4L LL</t>
+          <t>Viscogen KL 23, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1432">
       <c r="A1432" s="4" t="inlineStr">
         <is>
-          <t>14CAE3</t>
+          <t>14E1F8</t>
         </is>
       </c>
       <c r="B1432" s="5" t="inlineStr">
         <is>
-          <t>Viscogen KL 23, 208L E4</t>
+          <t>Viscogen KL 23, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1433">
       <c r="A1433" s="4" t="inlineStr">
         <is>
-          <t>14E1F8</t>
+          <t>14E1F9</t>
         </is>
       </c>
       <c r="B1433" s="5" t="inlineStr">
         <is>
-          <t>Viscogen KL 23, 20L E4</t>
+          <t>Viscogen KL 23, 5L E4</t>
         </is>
       </c>
     </row>
     <row r="1434">
       <c r="A1434" s="4" t="inlineStr">
         <is>
-          <t>14E1F9</t>
+          <t>15B5AB</t>
         </is>
       </c>
       <c r="B1434" s="5" t="inlineStr">
         <is>
-          <t>Viscogen KL 23, 5L E4</t>
+          <t>Viscogen KL 3 Spray, 12X.4L KL</t>
         </is>
       </c>
     </row>
     <row r="1435">
       <c r="A1435" s="4" t="inlineStr">
         <is>
-          <t>15B5AB</t>
+          <t>14CAF8</t>
         </is>
       </c>
       <c r="B1435" s="5" t="inlineStr">
         <is>
-          <t>Viscogen KL 3 Spray, 12X.4L KL</t>
+          <t>Viscogen KL 3, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1436">
       <c r="A1436" s="4" t="inlineStr">
         <is>
-          <t>14CAF8</t>
+          <t>14E317</t>
         </is>
       </c>
       <c r="B1436" s="5" t="inlineStr">
         <is>
-          <t>Viscogen KL 3, 208L E4</t>
+          <t>Viscogen KL 3, 20L E7</t>
         </is>
       </c>
     </row>
     <row r="1437">
       <c r="A1437" s="4" t="inlineStr">
         <is>
-          <t>14E317</t>
+          <t>15B166</t>
         </is>
       </c>
       <c r="B1437" s="5" t="inlineStr">
         <is>
-          <t>Viscogen KL 3, 20L E7</t>
+          <t>Viscogen KL 3, 5L E4</t>
         </is>
       </c>
     </row>
     <row r="1438">
       <c r="A1438" s="4" t="inlineStr">
         <is>
-          <t>15B166</t>
+          <t>15E1BF</t>
         </is>
       </c>
       <c r="B1438" s="5" t="inlineStr">
         <is>
-          <t>Viscogen KL 3, 5L E4</t>
+          <t>Viscogen KL 300 Spray, 12X.4L LO</t>
         </is>
       </c>
     </row>
     <row r="1439">
       <c r="A1439" s="4" t="inlineStr">
         <is>
-          <t>15E1BF</t>
+          <t>15B167</t>
         </is>
       </c>
       <c r="B1439" s="5" t="inlineStr">
         <is>
-          <t>Viscogen KL 300 Spray, 12X.4L LO</t>
+          <t>Viscogen KL 300, 5L E4</t>
         </is>
       </c>
     </row>
     <row r="1440">
       <c r="A1440" s="4" t="inlineStr">
         <is>
-          <t>15B167</t>
+          <t>14C61F</t>
         </is>
       </c>
       <c r="B1440" s="5" t="inlineStr">
         <is>
-          <t>Viscogen KL 300, 5L E4</t>
+          <t>Viscogen KL 9, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1441">
       <c r="A1441" s="4" t="inlineStr">
         <is>
-          <t>14C61F</t>
+          <t>121852</t>
         </is>
       </c>
       <c r="B1441" s="5" t="inlineStr">
         <is>
-          <t>Viscogen KL 9, 208L E4</t>
+          <t>Viscogen KL 9, 20L E7</t>
         </is>
       </c>
     </row>
     <row r="1442">
       <c r="A1442" s="4" t="inlineStr">
         <is>
-          <t>121852</t>
+          <t>153B81</t>
         </is>
       </c>
       <c r="B1442" s="5" t="inlineStr">
         <is>
-          <t>Viscogen KL 9, 20L E7</t>
+          <t>Viscogen KL 9, 5L E4</t>
         </is>
       </c>
     </row>
     <row r="1443">
       <c r="A1443" s="4" t="inlineStr">
         <is>
-          <t>153B81</t>
+          <t>152A97</t>
         </is>
       </c>
       <c r="B1443" s="5" t="inlineStr">
         <is>
-          <t>Viscogen KL 9, 5L E4</t>
+          <t>Viscogen KLK 25, 1000L E4</t>
         </is>
       </c>
     </row>
     <row r="1444">
       <c r="A1444" s="4" t="inlineStr">
         <is>
-          <t>152A97</t>
+          <t>14CB0D</t>
         </is>
       </c>
       <c r="B1444" s="5" t="inlineStr">
         <is>
-          <t>Viscogen KLK 25, 1000L E4</t>
+          <t>Viscogen KLK 25, 208L E4</t>
         </is>
       </c>
     </row>
     <row r="1445">
       <c r="A1445" s="4" t="inlineStr">
         <is>
-          <t>14CB0D</t>
+          <t>152A98</t>
         </is>
       </c>
       <c r="B1445" s="5" t="inlineStr">
         <is>
-          <t>Viscogen KLK 25, 208L E4</t>
+          <t>Viscogen KLK 25, 20L E4</t>
         </is>
       </c>
     </row>
     <row r="1446">
       <c r="A1446" s="4" t="inlineStr">
         <is>
-          <t>152A98</t>
+          <t>152A89</t>
         </is>
       </c>
       <c r="B1446" s="5" t="inlineStr">
         <is>
-          <t>Viscogen KLK 25, 20L E4</t>
+          <t>Viscogen KLK 28, 1000L E4</t>
         </is>
       </c>
     </row>
     <row r="1447">
       <c r="A1447" s="4" t="inlineStr">
         <is>
-          <t>152A89</t>
+          <t>14CB0F</t>
         </is>
       </c>
       <c r="B1447" s="5" t="inlineStr">
-        <is>
-          <t>Viscogen KLK 28, 1000L E4</t>
-        </is>
-      </c>
-    </row>
-    <row r="1448">
-      <c r="A1448" s="4" t="inlineStr">
-        <is>
-          <t>14CB0F</t>
-        </is>
-      </c>
-      <c r="B1448" s="5" t="inlineStr">
         <is>
           <t>Viscogen KLK 28, 208L E4</t>
         </is>
